--- a/CB1-revision-planner.xlsx
+++ b/CB1-revision-planner.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start here" sheetId="1" r:id="R379d915d174a4148"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Weekly plan" sheetId="2" r:id="Ra574e1b0c8eb4233"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Topic confidence" sheetId="3" r:id="R50c15fe096784590"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mistake log" sheetId="4" r:id="R9065fea0e39d4c5f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Plan data" sheetId="5" r:id="R46a41e4111ae4cfd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start here" sheetId="1" r:id="R4d491d41c0584c2a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Weekly plan" sheetId="2" r:id="Rb12e4e1786fa417a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Topic confidence" sheetId="3" r:id="Rcad590cfecfd47b6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mistake log" sheetId="4" r:id="R6b38db19c9404500"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Plan data" sheetId="5" r:id="Rbfa42755885d437f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -849,7 +849,7 @@
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
       <x:c r="A1" s="154" t="str">
-        <x:v>CM1 Flexible Revision Planner</x:v>
+        <x:v>CB1 Flexible Revision Planner</x:v>
       </x:c>
       <x:c r="B1" s="155"/>
       <x:c r="C1" s="155"/>
@@ -871,7 +871,7 @@
     </x:row>
     <x:row r="3" ht="28" customHeight="1">
       <x:c r="A3" s="12" t="str">
-        <x:v>A simple plan for deciding what to revise each week - without turning planning into another job.</x:v>
+        <x:v>A simple plan for keeping a broad syllabus focused on active recall, questions and written-answer practice.</x:v>
       </x:c>
       <x:c r="B3" s="12"/>
       <x:c r="C3" s="12"/>
@@ -1108,7 +1108,7 @@
         <x:v>IFoA total study-hours benchmark</x:v>
       </x:c>
       <x:c r="B21" s="135" t="n">
-        <x:v>250</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="C21" s="118"/>
       <x:c r="D21" s="125" t="str">
@@ -1116,7 +1116,7 @@
       </x:c>
       <x:c r="E21" s="137" t="n">
         <x:f>MAX(0,B21-B22)</x:f>
-        <x:v>250</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="F21" s="4"/>
       <x:c r="G21" s="4"/>
@@ -1135,7 +1135,7 @@
       </x:c>
       <x:c r="E22" s="138" t="n">
         <x:f>IF(B18&gt;0,E21/B18,"")</x:f>
-        <x:v>31.25</x:v>
+        <x:v>18.75</x:v>
       </x:c>
       <x:c r="F22" s="4"/>
       <x:c r="G22" s="4"/>
@@ -1143,7 +1143,7 @@
     </x:row>
     <x:row r="23" ht="34" customHeight="1">
       <x:c r="A23" s="165" t="str">
-        <x:v>Keep Excel practice running alongside written work. Don't leave Paper B-style practice until the end.</x:v>
+        <x:v>Avoid spending the whole revision period rereading notes. Practise producing concise, applied written answers every week.</x:v>
       </x:c>
       <x:c r="B23" s="165"/>
       <x:c r="C23" s="165"/>
@@ -1155,7 +1155,7 @@
     </x:row>
     <x:row r="24" ht="34" customHeight="1">
       <x:c r="A24" s="167" t="str">
-        <x:v>IFoA recommends 250 study hours for CM1 overall. This is a full-subject benchmark, not a requirement for your final revision window. Oliver's note: I found tracking the recommended total useful because it stopped me underestimating how much time the subject needed.</x:v>
+        <x:v>IFoA recommends 150 study hours for CB1 overall. This is a full-subject benchmark, not a requirement for your final revision window. Oliver's note: I found tracking the recommended total useful because it stopped me underestimating how much time the subject needed.</x:v>
       </x:c>
       <x:c r="B24" s="167"/>
       <x:c r="C24" s="167"/>
@@ -1421,7 +1421,7 @@
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
       <x:c r="A1" s="64" t="str">
-        <x:v>CM1 weekly revision plan</x:v>
+        <x:v>CB1 weekly revision plan</x:v>
       </x:c>
       <x:c r="B1" s="4"/>
       <x:c r="C1" s="4"/>
@@ -1483,7 +1483,7 @@
         <x:v>Question practice</x:v>
       </x:c>
       <x:c r="G5" s="70" t="str">
-        <x:v>Excel / applied practice</x:v>
+        <x:v>Applied practice</x:v>
       </x:c>
       <x:c r="H5" s="70" t="str">
         <x:v>Status</x:v>
@@ -1499,23 +1499,23 @@
       </x:c>
       <x:c r="C6" s="78" t="str">
         <x:f>IF(A6="","",IFERROR(VLOOKUP('Start here'!$B$18&amp;"|"&amp;A6,'_Plan data'!$A$2:$I$131,4,FALSE),""))</x:f>
-        <x:v>Theory of interest rates</x:v>
+        <x:v>Governance and objectives</x:v>
       </x:c>
       <x:c r="D6" s="78" t="str">
         <x:f>IF(A6="","",IFERROR(VLOOKUP('Start here'!$B$18&amp;"|"&amp;A6,'_Plan data'!$A$2:$I$131,5,FALSE),""))</x:f>
-        <x:v>Rate conversions, discount functions, force of interest and term structures</x:v>
+        <x:v>Corporate governance, ethics, stakeholders and shareholder wealth</x:v>
       </x:c>
       <x:c r="E6" s="78" t="str">
         <x:f>IF(A6="","",IFERROR(VLOOKUP('Start here'!$B$18&amp;"|"&amp;A6,'_Plan data'!$A$2:$I$131,6,FALSE),""))</x:f>
-        <x:v>Build a one-page rate-conversion sheet and derive each relationship once.</x:v>
+        <x:v>Create a stakeholder-conflict grid and a governance answer plan.</x:v>
       </x:c>
       <x:c r="F6" s="78" t="str">
         <x:f>IF(A6="","",IFERROR(VLOOKUP('Start here'!$B$18&amp;"|"&amp;A6,'_Plan data'!$A$2:$I$131,7,FALSE),""))</x:f>
-        <x:v>Complete short calculations and mark units and timing explicitly.</x:v>
+        <x:v>Write short applied explanations and self-check for a direct conclusion.</x:v>
       </x:c>
       <x:c r="G6" s="78" t="str">
         <x:f>IF(A6="","",IFERROR(VLOOKUP('Start here'!$B$18&amp;"|"&amp;A6,'_Plan data'!$A$2:$I$131,8,FALSE),""))</x:f>
-        <x:v>Create a simple cashflow-discounting model in Excel.</x:v>
+        <x:v>Build a one-page summary of key distinctions and common command words.</x:v>
       </x:c>
       <x:c r="H6" s="80" t="str"/>
     </x:row>
@@ -1529,23 +1529,23 @@
       </x:c>
       <x:c r="C7" s="78" t="str">
         <x:f>IF(A7="","",IFERROR(VLOOKUP('Start here'!$B$18&amp;"|"&amp;A7,'_Plan data'!$A$2:$I$131,4,FALSE),""))</x:f>
-        <x:v>Equation of value and loans</x:v>
+        <x:v>Business ownership and taxation</x:v>
       </x:c>
       <x:c r="D7" s="78" t="str">
         <x:f>IF(A7="","",IFERROR(VLOOKUP('Start here'!$B$18&amp;"|"&amp;A7,'_Plan data'!$A$2:$I$131,5,FALSE),""))</x:f>
-        <x:v>Cashflow valuation, loans, outstanding balances, bonds and yield</x:v>
+        <x:v>Business forms, ownership, tax and corporate structure</x:v>
       </x:c>
       <x:c r="E7" s="78" t="str">
         <x:f>IF(A7="","",IFERROR(VLOOKUP('Start here'!$B$18&amp;"|"&amp;A7,'_Plan data'!$A$2:$I$131,6,FALSE),""))</x:f>
-        <x:v>Draw every cashflow timeline before calculating and practise two methods for loan questions.</x:v>
+        <x:v>Compare each legal form by ownership, risk, capital and control.</x:v>
       </x:c>
       <x:c r="F7" s="78" t="str">
         <x:f>IF(A7="","",IFERROR(VLOOKUP('Start here'!$B$18&amp;"|"&amp;A7,'_Plan data'!$A$2:$I$131,7,FALSE),""))</x:f>
-        <x:v>Complete mixed loan and bond questions under time pressure.</x:v>
+        <x:v>Complete scenario questions requiring a justified recommendation.</x:v>
       </x:c>
       <x:c r="G7" s="78" t="str">
         <x:f>IF(A7="","",IFERROR(VLOOKUP('Start here'!$B$18&amp;"|"&amp;A7,'_Plan data'!$A$2:$I$131,8,FALSE),""))</x:f>
-        <x:v>Build a loan schedule with a rate input and balance check.</x:v>
+        <x:v>Use a simple table to compare tax or cashflow implications.</x:v>
       </x:c>
       <x:c r="H7" s="80" t="str"/>
     </x:row>
@@ -1559,23 +1559,23 @@
       </x:c>
       <x:c r="C8" s="78" t="str">
         <x:f>IF(A8="","",IFERROR(VLOOKUP('Start here'!$B$18&amp;"|"&amp;A8,'_Plan data'!$A$2:$I$131,4,FALSE),""))</x:f>
-        <x:v>Annuities and duration</x:v>
+        <x:v>Raising finance</x:v>
       </x:c>
       <x:c r="D8" s="78" t="str">
         <x:f>IF(A8="","",IFERROR(VLOOKUP('Start here'!$B$18&amp;"|"&amp;A8,'_Plan data'!$A$2:$I$131,5,FALSE),""))</x:f>
-        <x:v>Level and increasing annuities, immunisation and duration concepts</x:v>
+        <x:v>Long and short-term finance, share issues, debt, leasing and working capital</x:v>
       </x:c>
       <x:c r="E8" s="78" t="str">
         <x:f>IF(A8="","",IFERROR(VLOOKUP('Start here'!$B$18&amp;"|"&amp;A8,'_Plan data'!$A$2:$I$131,6,FALSE),""))</x:f>
-        <x:v>Create a formula map and a list of common timing traps.</x:v>
+        <x:v>Create a finance-source comparison: cost, risk, control, flexibility and timing.</x:v>
       </x:c>
       <x:c r="F8" s="78" t="str">
         <x:f>IF(A8="","",IFERROR(VLOOKUP('Start here'!$B$18&amp;"|"&amp;A8,'_Plan data'!$A$2:$I$131,7,FALSE),""))</x:f>
-        <x:v>Attempt a timed mixed interest-rate set.</x:v>
+        <x:v>Complete finance-choice questions with a stated recommendation.</x:v>
       </x:c>
       <x:c r="G8" s="78" t="str">
         <x:f>IF(A8="","",IFERROR(VLOOKUP('Start here'!$B$18&amp;"|"&amp;A8,'_Plan data'!$A$2:$I$131,8,FALSE),""))</x:f>
-        <x:v>Use Excel to compare present values under alternative interest-rate scenarios.</x:v>
+        <x:v>Calculate a lease or short-term financing comparison.</x:v>
       </x:c>
       <x:c r="H8" s="80" t="str"/>
     </x:row>
@@ -1589,23 +1589,23 @@
       </x:c>
       <x:c r="C9" s="78" t="str">
         <x:f>IF(A9="","",IFERROR(VLOOKUP('Start here'!$B$18&amp;"|"&amp;A9,'_Plan data'!$A$2:$I$131,4,FALSE),""))</x:f>
-        <x:v>Single-life models</x:v>
+        <x:v>Accounts foundations</x:v>
       </x:c>
       <x:c r="D9" s="78" t="str">
         <x:f>IF(A9="","",IFERROR(VLOOKUP('Start here'!$B$18&amp;"|"&amp;A9,'_Plan data'!$A$2:$I$131,5,FALSE),""))</x:f>
-        <x:v>Survival probabilities, life tables, assurance and annuity values</x:v>
+        <x:v>Statement of profit or loss, financial position and cash flows</x:v>
       </x:c>
       <x:c r="E9" s="78" t="str">
         <x:f>IF(A9="","",IFERROR(VLOOKUP('Start here'!$B$18&amp;"|"&amp;A9,'_Plan data'!$A$2:$I$131,6,FALSE),""))</x:f>
-        <x:v>Convert symbols to a timeline and annotate the contingent payment condition.</x:v>
+        <x:v>Reconstruct the three statements from a blank template.</x:v>
       </x:c>
       <x:c r="F9" s="78" t="str">
         <x:f>IF(A9="","",IFERROR(VLOOKUP('Start here'!$B$18&amp;"|"&amp;A9,'_Plan data'!$A$2:$I$131,7,FALSE),""))</x:f>
-        <x:v>Practise life-contingency questions and rewrite any weak setup.</x:v>
+        <x:v>Complete an accounts-building question and reconcile every total.</x:v>
       </x:c>
       <x:c r="G9" s="78" t="str">
         <x:f>IF(A9="","",IFERROR(VLOOKUP('Start here'!$B$18&amp;"|"&amp;A9,'_Plan data'!$A$2:$I$131,8,FALSE),""))</x:f>
-        <x:v>Calculate life annuity values from a supplied table.</x:v>
+        <x:v>Create an accounts template with balance checks.</x:v>
       </x:c>
       <x:c r="H9" s="80" t="str"/>
     </x:row>
@@ -1619,23 +1619,23 @@
       </x:c>
       <x:c r="C10" s="78" t="str">
         <x:f>IF(A10="","",IFERROR(VLOOKUP('Start here'!$B$18&amp;"|"&amp;A10,'_Plan data'!$A$2:$I$131,4,FALSE),""))</x:f>
-        <x:v>Multiple lives and decrements</x:v>
+        <x:v>Accounts construction and groups</x:v>
       </x:c>
       <x:c r="D10" s="78" t="str">
         <x:f>IF(A10="","",IFERROR(VLOOKUP('Start here'!$B$18&amp;"|"&amp;A10,'_Plan data'!$A$2:$I$131,5,FALSE),""))</x:f>
-        <x:v>Joint-life, last-survivor, multiple-decrement and select models</x:v>
+        <x:v>Adjustments, group accounts, insurance and bank accounts</x:v>
       </x:c>
       <x:c r="E10" s="78" t="str">
         <x:f>IF(A10="","",IFERROR(VLOOKUP('Start here'!$B$18&amp;"|"&amp;A10,'_Plan data'!$A$2:$I$131,6,FALSE),""))</x:f>
-        <x:v>Write a decision tree for the status and payment trigger.</x:v>
+        <x:v>Write an adjustment checklist before starting any construction question.</x:v>
       </x:c>
       <x:c r="F10" s="78" t="str">
         <x:f>IF(A10="","",IFERROR(VLOOKUP('Start here'!$B$18&amp;"|"&amp;A10,'_Plan data'!$A$2:$I$131,7,FALSE),""))</x:f>
-        <x:v>Attempt a longer multi-part question and audit the notation.</x:v>
+        <x:v>Attempt a longer multi-part construction question.</x:v>
       </x:c>
       <x:c r="G10" s="78" t="str">
         <x:f>IF(A10="","",IFERROR(VLOOKUP('Start here'!$B$18&amp;"|"&amp;A10,'_Plan data'!$A$2:$I$131,8,FALSE),""))</x:f>
-        <x:v>Model decrement probabilities and test that probabilities reconcile.</x:v>
+        <x:v>Use a spreadsheet to separate adjustments from final statements.</x:v>
       </x:c>
       <x:c r="H10" s="80" t="str"/>
     </x:row>
@@ -1649,23 +1649,23 @@
       </x:c>
       <x:c r="C11" s="78" t="str">
         <x:f>IF(A11="","",IFERROR(VLOOKUP('Start here'!$B$18&amp;"|"&amp;A11,'_Plan data'!$A$2:$I$131,4,FALSE),""))</x:f>
-        <x:v>Pricing and reserving</x:v>
+        <x:v>Interpreting accounts</x:v>
       </x:c>
       <x:c r="D11" s="78" t="str">
         <x:f>IF(A11="","",IFERROR(VLOOKUP('Start here'!$B$18&amp;"|"&amp;A11,'_Plan data'!$A$2:$I$131,5,FALSE),""))</x:f>
-        <x:v>Net premiums, gross premiums, prospective and retrospective reserves</x:v>
+        <x:v>Ratios, trends, limitations and investor analysis</x:v>
       </x:c>
       <x:c r="E11" s="78" t="str">
         <x:f>IF(A11="","",IFERROR(VLOOKUP('Start here'!$B$18&amp;"|"&amp;A11,'_Plan data'!$A$2:$I$131,6,FALSE),""))</x:f>
-        <x:v>For each formula, state what is being valued, at what time and on what basis.</x:v>
+        <x:v>Use a claim-evidence-conclusion structure for every interpretation paragraph.</x:v>
       </x:c>
       <x:c r="F11" s="78" t="str">
         <x:f>IF(A11="","",IFERROR(VLOOKUP('Start here'!$B$18&amp;"|"&amp;A11,'_Plan data'!$A$2:$I$131,7,FALSE),""))</x:f>
-        <x:v>Complete premium and reserve questions to a strict time budget.</x:v>
+        <x:v>Complete a ratio question, then improve the quality of the narrative answer.</x:v>
       </x:c>
       <x:c r="G11" s="78" t="str">
         <x:f>IF(A11="","",IFERROR(VLOOKUP('Start here'!$B$18&amp;"|"&amp;A11,'_Plan data'!$A$2:$I$131,8,FALSE),""))</x:f>
-        <x:v>Build a reserve roll-forward and investigate each movement.</x:v>
+        <x:v>Calculate and graph a ratio trend from a small data table.</x:v>
       </x:c>
       <x:c r="H11" s="80" t="str"/>
     </x:row>
@@ -1679,23 +1679,23 @@
       </x:c>
       <x:c r="C12" s="78" t="str">
         <x:f>IF(A12="","",IFERROR(VLOOKUP('Start here'!$B$18&amp;"|"&amp;A12,'_Plan data'!$A$2:$I$131,4,FALSE),""))</x:f>
-        <x:v>Integrated exam practice</x:v>
+        <x:v>Capital structure and growth</x:v>
       </x:c>
       <x:c r="D12" s="78" t="str">
         <x:f>IF(A12="","",IFERROR(VLOOKUP('Start here'!$B$18&amp;"|"&amp;A12,'_Plan data'!$A$2:$I$131,5,FALSE),""))</x:f>
-        <x:v>Mixed CM1 applications, answer structure and weak-area repair</x:v>
+        <x:v>Derivatives, restructuring, WACC, dividend policy and acquisition</x:v>
       </x:c>
       <x:c r="E12" s="78" t="str">
         <x:f>IF(A12="","",IFERROR(VLOOKUP('Start here'!$B$18&amp;"|"&amp;A12,'_Plan data'!$A$2:$I$131,6,FALSE),""))</x:f>
-        <x:v>Choose three recurring error themes and revisit them before comfortable topics.</x:v>
+        <x:v>Create a decision tree for financing and restructuring recommendations.</x:v>
       </x:c>
       <x:c r="F12" s="78" t="str">
         <x:f>IF(A12="","",IFERROR(VLOOKUP('Start here'!$B$18&amp;"|"&amp;A12,'_Plan data'!$A$2:$I$131,7,FALSE),""))</x:f>
-        <x:v>Complete a substantial timed Paper A-style set and self-mark your method.</x:v>
+        <x:v>Complete applied finance questions including a WACC calculation.</x:v>
       </x:c>
       <x:c r="G12" s="78" t="str">
         <x:f>IF(A12="","",IFERROR(VLOOKUP('Start here'!$B$18&amp;"|"&amp;A12,'_Plan data'!$A$2:$I$131,8,FALSE),""))</x:f>
-        <x:v>Complete a timed Excel challenge and check formulas independently.</x:v>
+        <x:v>Build a WACC sensitivity table.</x:v>
       </x:c>
       <x:c r="H12" s="80" t="str"/>
     </x:row>
@@ -1709,23 +1709,23 @@
       </x:c>
       <x:c r="C13" s="78" t="str">
         <x:f>IF(A13="","",IFERROR(VLOOKUP('Start here'!$B$18&amp;"|"&amp;A13,'_Plan data'!$A$2:$I$131,4,FALSE),""))</x:f>
-        <x:v>Mock and consolidation</x:v>
+        <x:v>Project appraisal and mock</x:v>
       </x:c>
       <x:c r="D13" s="78" t="str">
         <x:f>IF(A13="","",IFERROR(VLOOKUP('Start here'!$B$18&amp;"|"&amp;A13,'_Plan data'!$A$2:$I$131,5,FALSE),""))</x:f>
-        <x:v>Whole syllabus, timed practice and final weak-area repair</x:v>
+        <x:v>NPV, IRR, risk, capital projects and whole-syllabus consolidation</x:v>
       </x:c>
       <x:c r="E13" s="78" t="str">
         <x:f>IF(A13="","",IFERROR(VLOOKUP('Start here'!$B$18&amp;"|"&amp;A13,'_Plan data'!$A$2:$I$131,6,FALSE),""))</x:f>
-        <x:v>Create a final formula and notation sheet from memory, then correct it.</x:v>
+        <x:v>Prepare an investment-appraisal checklist and a final error list.</x:v>
       </x:c>
       <x:c r="F13" s="78" t="str">
         <x:f>IF(A13="","",IFERROR(VLOOKUP('Start here'!$B$18&amp;"|"&amp;A13,'_Plan data'!$A$2:$I$131,7,FALSE),""))</x:f>
-        <x:v>Sit a full mock or equivalent timed set, then separate marking from error correction.</x:v>
+        <x:v>Complete a timed mock or equivalent mixed set, then redraft weak written answers.</x:v>
       </x:c>
       <x:c r="G13" s="78" t="str">
         <x:f>IF(A13="","",IFERROR(VLOOKUP('Start here'!$B$18&amp;"|"&amp;A13,'_Plan data'!$A$2:$I$131,8,FALSE),""))</x:f>
-        <x:v>Rebuild the weakest modelling task from a blank workbook.</x:v>
+        <x:v>Build an NPV model and test a key sensitivity.</x:v>
       </x:c>
       <x:c r="H13" s="80" t="str"/>
     </x:row>
@@ -2025,7 +2025,7 @@
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
       <x:c r="A1" s="64" t="str">
-        <x:v>CM1 topic confidence</x:v>
+        <x:v>CB1 topic confidence</x:v>
       </x:c>
       <x:c r="B1" s="4"/>
       <x:c r="C1" s="4"/>
@@ -2067,80 +2067,80 @@
     </x:row>
     <x:row r="6" ht="38" customHeight="1">
       <x:c r="A6" s="58" t="str">
-        <x:v>Theory of interest rates</x:v>
+        <x:v>Governance and objectives</x:v>
       </x:c>
       <x:c r="B6" s="58" t="str">
-        <x:v>Rate conversions, discount functions, force of interest and term structures</x:v>
+        <x:v>Corporate governance, ethics, stakeholders and shareholder wealth</x:v>
       </x:c>
       <x:c r="C6" s="90" t="str"/>
       <x:c r="D6" s="90" t="str"/>
     </x:row>
     <x:row r="7" ht="38" customHeight="1">
       <x:c r="A7" s="58" t="str">
-        <x:v>Equation of value and loans</x:v>
+        <x:v>Business ownership and taxation</x:v>
       </x:c>
       <x:c r="B7" s="58" t="str">
-        <x:v>Cashflow valuation, loans, outstanding balances, bonds and yield</x:v>
+        <x:v>Business forms, ownership, tax and corporate structure</x:v>
       </x:c>
       <x:c r="C7" s="90" t="str"/>
       <x:c r="D7" s="90" t="str"/>
     </x:row>
     <x:row r="8" ht="38" customHeight="1">
       <x:c r="A8" s="58" t="str">
-        <x:v>Annuities and duration</x:v>
+        <x:v>Raising finance</x:v>
       </x:c>
       <x:c r="B8" s="58" t="str">
-        <x:v>Level and increasing annuities, immunisation and duration concepts</x:v>
+        <x:v>Long and short-term finance, share issues, debt, leasing and working capital</x:v>
       </x:c>
       <x:c r="C8" s="90" t="str"/>
       <x:c r="D8" s="90" t="str"/>
     </x:row>
     <x:row r="9" ht="38" customHeight="1">
       <x:c r="A9" s="58" t="str">
-        <x:v>Single-life models</x:v>
+        <x:v>Accounts foundations</x:v>
       </x:c>
       <x:c r="B9" s="58" t="str">
-        <x:v>Survival probabilities, life tables, assurance and annuity values</x:v>
+        <x:v>Statement of profit or loss, financial position and cash flows</x:v>
       </x:c>
       <x:c r="C9" s="90" t="str"/>
       <x:c r="D9" s="90" t="str"/>
     </x:row>
     <x:row r="10" ht="38" customHeight="1">
       <x:c r="A10" s="58" t="str">
-        <x:v>Multiple lives and decrements</x:v>
+        <x:v>Accounts construction and groups</x:v>
       </x:c>
       <x:c r="B10" s="58" t="str">
-        <x:v>Joint-life, last-survivor, multiple-decrement and select models</x:v>
+        <x:v>Adjustments, group accounts, insurance and bank accounts</x:v>
       </x:c>
       <x:c r="C10" s="90" t="str"/>
       <x:c r="D10" s="90" t="str"/>
     </x:row>
     <x:row r="11" ht="38" customHeight="1">
       <x:c r="A11" s="58" t="str">
-        <x:v>Pricing and reserving</x:v>
+        <x:v>Interpreting accounts</x:v>
       </x:c>
       <x:c r="B11" s="58" t="str">
-        <x:v>Net premiums, gross premiums, prospective and retrospective reserves</x:v>
+        <x:v>Ratios, trends, limitations and investor analysis</x:v>
       </x:c>
       <x:c r="C11" s="90" t="str"/>
       <x:c r="D11" s="90" t="str"/>
     </x:row>
     <x:row r="12" ht="38" customHeight="1">
       <x:c r="A12" s="58" t="str">
-        <x:v>Integrated exam practice</x:v>
+        <x:v>Capital structure and growth</x:v>
       </x:c>
       <x:c r="B12" s="58" t="str">
-        <x:v>Mixed CM1 applications, answer structure and weak-area repair</x:v>
+        <x:v>Derivatives, restructuring, WACC, dividend policy and acquisition</x:v>
       </x:c>
       <x:c r="C12" s="90" t="str"/>
       <x:c r="D12" s="90" t="str"/>
     </x:row>
     <x:row r="13" ht="38" customHeight="1">
       <x:c r="A13" s="92" t="str">
-        <x:v>Mock and consolidation</x:v>
+        <x:v>Project appraisal and mock</x:v>
       </x:c>
       <x:c r="B13" s="92" t="str">
-        <x:v>Whole syllabus, timed practice and final weak-area repair</x:v>
+        <x:v>NPV, IRR, risk, capital projects and whole-syllabus consolidation</x:v>
       </x:c>
       <x:c r="C13" s="93" t="str"/>
       <x:c r="D13" s="93" t="str"/>
@@ -2250,7 +2250,7 @@
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
       <x:c r="A1" s="64" t="str">
-        <x:v>CM1 mistake log</x:v>
+        <x:v>CB1 mistake log</x:v>
       </x:c>
       <x:c r="B1" s="4"/>
       <x:c r="C1" s="4"/>
@@ -2655,22 +2655,22 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="D2" s="109" t="str">
-        <x:v>Theory of interest rates + Equation of value and loans</x:v>
+        <x:v>Governance and objectives + Business ownership and taxation</x:v>
       </x:c>
       <x:c r="E2" s="109" t="str">
-        <x:v>Rate conversions, discount functions, force of interest and term structures; Cashflow valuation, loans, outstanding balances, bonds and yield</x:v>
+        <x:v>Corporate governance, ethics, stakeholders and shareholder wealth; Business forms, ownership, tax and corporate structure</x:v>
       </x:c>
       <x:c r="F2" s="109" t="str">
-        <x:v>Cover both blocks deliberately: Build a one-page rate-conversion sheet and derive each relationship once. Then Draw every cashflow timeline before calculating and practise two methods for loan questions.</x:v>
+        <x:v>Cover both blocks deliberately: Create a stakeholder-conflict grid and a governance answer plan. Then Compare each legal form by ownership, risk, capital and control.</x:v>
       </x:c>
       <x:c r="G2" s="109" t="str">
-        <x:v>Prioritise mixed practice across both blocks: Complete short calculations and mark units and timing explicitly. Then Complete mixed loan and bond questions under time pressure.</x:v>
+        <x:v>Prioritise mixed practice across both blocks: Write short applied explanations and self-check for a direct conclusion. Then Complete scenario questions requiring a justified recommendation.</x:v>
       </x:c>
       <x:c r="H2" s="109" t="str">
-        <x:v>Applied practice: Create a simple cashflow-discounting model in Excel. Then Build a loan schedule with a rate input and balance check.</x:v>
+        <x:v>Applied practice: Build a one-page summary of key distinctions and common command words. Then Use a simple table to compare tax or cashflow implications.</x:v>
       </x:c>
       <x:c r="I2" s="109" t="n">
-        <x:v>38</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="J2" s="109"/>
       <x:c r="K2" s="109"/>
@@ -2686,19 +2686,19 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="D3" s="109" t="str">
-        <x:v>Annuities and duration + Single-life models</x:v>
+        <x:v>Raising finance + Accounts foundations</x:v>
       </x:c>
       <x:c r="E3" s="109" t="str">
-        <x:v>Level and increasing annuities, immunisation and duration concepts; Survival probabilities, life tables, assurance and annuity values</x:v>
+        <x:v>Long and short-term finance, share issues, debt, leasing and working capital; Statement of profit or loss, financial position and cash flows</x:v>
       </x:c>
       <x:c r="F3" s="109" t="str">
-        <x:v>Cover both blocks deliberately: Create a formula map and a list of common timing traps. Then Convert symbols to a timeline and annotate the contingent payment condition.</x:v>
+        <x:v>Cover both blocks deliberately: Create a finance-source comparison: cost, risk, control, flexibility and timing. Then Reconstruct the three statements from a blank template.</x:v>
       </x:c>
       <x:c r="G3" s="109" t="str">
-        <x:v>Prioritise mixed practice across both blocks: Attempt a timed mixed interest-rate set. Then Practise life-contingency questions and rewrite any weak setup.</x:v>
+        <x:v>Prioritise mixed practice across both blocks: Complete finance-choice questions with a stated recommendation. Then Complete an accounts-building question and reconcile every total.</x:v>
       </x:c>
       <x:c r="H3" s="109" t="str">
-        <x:v>Applied practice: Use Excel to compare present values under alternative interest-rate scenarios. Then Calculate life annuity values from a supplied table.</x:v>
+        <x:v>Applied practice: Calculate a lease or short-term financing comparison. Then Create an accounts template with balance checks.</x:v>
       </x:c>
       <x:c r="I3" s="109" t="n">
         <x:v>38</x:v>
@@ -2717,19 +2717,19 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="D4" s="109" t="str">
-        <x:v>Multiple lives and decrements + Pricing and reserving</x:v>
+        <x:v>Accounts construction and groups + Interpreting accounts</x:v>
       </x:c>
       <x:c r="E4" s="109" t="str">
-        <x:v>Joint-life, last-survivor, multiple-decrement and select models; Net premiums, gross premiums, prospective and retrospective reserves</x:v>
+        <x:v>Adjustments, group accounts, insurance and bank accounts; Ratios, trends, limitations and investor analysis</x:v>
       </x:c>
       <x:c r="F4" s="109" t="str">
-        <x:v>Cover both blocks deliberately: Write a decision tree for the status and payment trigger. Then For each formula, state what is being valued, at what time and on what basis.</x:v>
+        <x:v>Cover both blocks deliberately: Write an adjustment checklist before starting any construction question. Then Use a claim-evidence-conclusion structure for every interpretation paragraph.</x:v>
       </x:c>
       <x:c r="G4" s="109" t="str">
-        <x:v>Prioritise mixed practice across both blocks: Attempt a longer multi-part question and audit the notation. Then Complete premium and reserve questions to a strict time budget.</x:v>
+        <x:v>Prioritise mixed practice across both blocks: Attempt a longer multi-part construction question. Then Complete a ratio question, then improve the quality of the narrative answer.</x:v>
       </x:c>
       <x:c r="H4" s="109" t="str">
-        <x:v>Applied practice: Model decrement probabilities and test that probabilities reconcile. Then Build a reserve roll-forward and investigate each movement.</x:v>
+        <x:v>Applied practice: Use a spreadsheet to separate adjustments from final statements. Then Calculate and graph a ratio trend from a small data table.</x:v>
       </x:c>
       <x:c r="I4" s="109" t="n">
         <x:v>38</x:v>
@@ -2748,22 +2748,22 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="D5" s="109" t="str">
-        <x:v>Integrated exam practice + Mock and consolidation</x:v>
+        <x:v>Capital structure and growth + Project appraisal and mock</x:v>
       </x:c>
       <x:c r="E5" s="109" t="str">
-        <x:v>Mixed CM1 applications, answer structure and weak-area repair; Whole syllabus, timed practice and final weak-area repair</x:v>
+        <x:v>Derivatives, restructuring, WACC, dividend policy and acquisition; NPV, IRR, risk, capital projects and whole-syllabus consolidation</x:v>
       </x:c>
       <x:c r="F5" s="109" t="str">
-        <x:v>Cover both blocks deliberately: Choose three recurring error themes and revisit them before comfortable topics. Then Create a final formula and notation sheet from memory, then correct it.</x:v>
+        <x:v>Cover both blocks deliberately: Create a decision tree for financing and restructuring recommendations. Then Prepare an investment-appraisal checklist and a final error list.</x:v>
       </x:c>
       <x:c r="G5" s="109" t="str">
-        <x:v>Prioritise mixed practice across both blocks: Complete a substantial timed Paper A-style set and self-mark your method. Then Sit a full mock or equivalent timed set, then separate marking from error correction.</x:v>
+        <x:v>Prioritise mixed practice across both blocks: Complete applied finance questions including a WACC calculation. Then Complete a timed mock or equivalent mixed set, then redraft weak written answers.</x:v>
       </x:c>
       <x:c r="H5" s="109" t="str">
-        <x:v>Applied practice: Complete a timed Excel challenge and check formulas independently. Then Rebuild the weakest modelling task from a blank workbook.</x:v>
+        <x:v>Applied practice: Build a WACC sensitivity table. Then Build an NPV model and test a key sensitivity.</x:v>
       </x:c>
       <x:c r="I5" s="109" t="n">
-        <x:v>55</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="J5" s="109"/>
       <x:c r="K5" s="109"/>
@@ -2779,22 +2779,22 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="D6" s="109" t="str">
-        <x:v>Theory of interest rates</x:v>
+        <x:v>Governance and objectives</x:v>
       </x:c>
       <x:c r="E6" s="109" t="str">
-        <x:v>Rate conversions, discount functions, force of interest and term structures</x:v>
+        <x:v>Corporate governance, ethics, stakeholders and shareholder wealth</x:v>
       </x:c>
       <x:c r="F6" s="109" t="str">
-        <x:v>Build a one-page rate-conversion sheet and derive each relationship once.</x:v>
+        <x:v>Create a stakeholder-conflict grid and a governance answer plan.</x:v>
       </x:c>
       <x:c r="G6" s="109" t="str">
-        <x:v>Complete short calculations and mark units and timing explicitly.</x:v>
+        <x:v>Write short applied explanations and self-check for a direct conclusion.</x:v>
       </x:c>
       <x:c r="H6" s="109" t="str">
-        <x:v>Create a simple cashflow-discounting model in Excel.</x:v>
+        <x:v>Build a one-page summary of key distinctions and common command words.</x:v>
       </x:c>
       <x:c r="I6" s="109" t="n">
-        <x:v>20</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="J6" s="109"/>
       <x:c r="K6" s="109"/>
@@ -2810,22 +2810,22 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="D7" s="109" t="str">
-        <x:v>Equation of value and loans + Annuities and duration</x:v>
+        <x:v>Business ownership and taxation + Raising finance</x:v>
       </x:c>
       <x:c r="E7" s="109" t="str">
-        <x:v>Cashflow valuation, loans, outstanding balances, bonds and yield; Level and increasing annuities, immunisation and duration concepts</x:v>
+        <x:v>Business forms, ownership, tax and corporate structure; Long and short-term finance, share issues, debt, leasing and working capital</x:v>
       </x:c>
       <x:c r="F7" s="109" t="str">
-        <x:v>Cover both blocks deliberately: Draw every cashflow timeline before calculating and practise two methods for loan questions. Then Create a formula map and a list of common timing traps.</x:v>
+        <x:v>Cover both blocks deliberately: Compare each legal form by ownership, risk, capital and control. Then Create a finance-source comparison: cost, risk, control, flexibility and timing.</x:v>
       </x:c>
       <x:c r="G7" s="109" t="str">
-        <x:v>Prioritise mixed practice across both blocks: Complete mixed loan and bond questions under time pressure. Then Attempt a timed mixed interest-rate set.</x:v>
+        <x:v>Prioritise mixed practice across both blocks: Complete scenario questions requiring a justified recommendation. Then Complete finance-choice questions with a stated recommendation.</x:v>
       </x:c>
       <x:c r="H7" s="109" t="str">
-        <x:v>Applied practice: Build a loan schedule with a rate input and balance check. Then Use Excel to compare present values under alternative interest-rate scenarios.</x:v>
+        <x:v>Applied practice: Use a simple table to compare tax or cashflow implications. Then Calculate a lease or short-term financing comparison.</x:v>
       </x:c>
       <x:c r="I7" s="109" t="n">
-        <x:v>36</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="J7" s="109"/>
       <x:c r="K7" s="109"/>
@@ -2841,22 +2841,22 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="D8" s="109" t="str">
-        <x:v>Single-life models</x:v>
+        <x:v>Accounts foundations</x:v>
       </x:c>
       <x:c r="E8" s="109" t="str">
-        <x:v>Survival probabilities, life tables, assurance and annuity values</x:v>
+        <x:v>Statement of profit or loss, financial position and cash flows</x:v>
       </x:c>
       <x:c r="F8" s="109" t="str">
-        <x:v>Convert symbols to a timeline and annotate the contingent payment condition.</x:v>
+        <x:v>Reconstruct the three statements from a blank template.</x:v>
       </x:c>
       <x:c r="G8" s="109" t="str">
-        <x:v>Practise life-contingency questions and rewrite any weak setup.</x:v>
+        <x:v>Complete an accounts-building question and reconcile every total.</x:v>
       </x:c>
       <x:c r="H8" s="109" t="str">
-        <x:v>Calculate life annuity values from a supplied table.</x:v>
+        <x:v>Create an accounts template with balance checks.</x:v>
       </x:c>
       <x:c r="I8" s="109" t="n">
-        <x:v>20</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="J8" s="109"/>
       <x:c r="K8" s="109"/>
@@ -2872,19 +2872,19 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="D9" s="109" t="str">
-        <x:v>Multiple lives and decrements + Pricing and reserving</x:v>
+        <x:v>Accounts construction and groups + Interpreting accounts</x:v>
       </x:c>
       <x:c r="E9" s="109" t="str">
-        <x:v>Joint-life, last-survivor, multiple-decrement and select models; Net premiums, gross premiums, prospective and retrospective reserves</x:v>
+        <x:v>Adjustments, group accounts, insurance and bank accounts; Ratios, trends, limitations and investor analysis</x:v>
       </x:c>
       <x:c r="F9" s="109" t="str">
-        <x:v>Cover both blocks deliberately: Write a decision tree for the status and payment trigger. Then For each formula, state what is being valued, at what time and on what basis.</x:v>
+        <x:v>Cover both blocks deliberately: Write an adjustment checklist before starting any construction question. Then Use a claim-evidence-conclusion structure for every interpretation paragraph.</x:v>
       </x:c>
       <x:c r="G9" s="109" t="str">
-        <x:v>Prioritise mixed practice across both blocks: Attempt a longer multi-part question and audit the notation. Then Complete premium and reserve questions to a strict time budget.</x:v>
+        <x:v>Prioritise mixed practice across both blocks: Attempt a longer multi-part construction question. Then Complete a ratio question, then improve the quality of the narrative answer.</x:v>
       </x:c>
       <x:c r="H9" s="109" t="str">
-        <x:v>Applied practice: Model decrement probabilities and test that probabilities reconcile. Then Build a reserve roll-forward and investigate each movement.</x:v>
+        <x:v>Applied practice: Use a spreadsheet to separate adjustments from final statements. Then Calculate and graph a ratio trend from a small data table.</x:v>
       </x:c>
       <x:c r="I9" s="109" t="n">
         <x:v>38</x:v>
@@ -2903,22 +2903,22 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="D10" s="109" t="str">
-        <x:v>Integrated exam practice + Mock and consolidation</x:v>
+        <x:v>Capital structure and growth + Project appraisal and mock</x:v>
       </x:c>
       <x:c r="E10" s="109" t="str">
-        <x:v>Mixed CM1 applications, answer structure and weak-area repair; Whole syllabus, timed practice and final weak-area repair</x:v>
+        <x:v>Derivatives, restructuring, WACC, dividend policy and acquisition; NPV, IRR, risk, capital projects and whole-syllabus consolidation</x:v>
       </x:c>
       <x:c r="F10" s="109" t="str">
-        <x:v>Cover both blocks deliberately: Choose three recurring error themes and revisit them before comfortable topics. Then Create a final formula and notation sheet from memory, then correct it.</x:v>
+        <x:v>Cover both blocks deliberately: Create a decision tree for financing and restructuring recommendations. Then Prepare an investment-appraisal checklist and a final error list.</x:v>
       </x:c>
       <x:c r="G10" s="109" t="str">
-        <x:v>Prioritise mixed practice across both blocks: Complete a substantial timed Paper A-style set and self-mark your method. Then Sit a full mock or equivalent timed set, then separate marking from error correction.</x:v>
+        <x:v>Prioritise mixed practice across both blocks: Complete applied finance questions including a WACC calculation. Then Complete a timed mock or equivalent mixed set, then redraft weak written answers.</x:v>
       </x:c>
       <x:c r="H10" s="109" t="str">
-        <x:v>Applied practice: Complete a timed Excel challenge and check formulas independently. Then Rebuild the weakest modelling task from a blank workbook.</x:v>
+        <x:v>Applied practice: Build a WACC sensitivity table. Then Build an NPV model and test a key sensitivity.</x:v>
       </x:c>
       <x:c r="I10" s="109" t="n">
-        <x:v>55</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="J10" s="109"/>
       <x:c r="K10" s="109"/>
@@ -2934,22 +2934,22 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="D11" s="109" t="str">
-        <x:v>Theory of interest rates</x:v>
+        <x:v>Governance and objectives</x:v>
       </x:c>
       <x:c r="E11" s="109" t="str">
-        <x:v>Rate conversions, discount functions, force of interest and term structures</x:v>
+        <x:v>Corporate governance, ethics, stakeholders and shareholder wealth</x:v>
       </x:c>
       <x:c r="F11" s="109" t="str">
-        <x:v>Build a one-page rate-conversion sheet and derive each relationship once.</x:v>
+        <x:v>Create a stakeholder-conflict grid and a governance answer plan.</x:v>
       </x:c>
       <x:c r="G11" s="109" t="str">
-        <x:v>Complete short calculations and mark units and timing explicitly.</x:v>
+        <x:v>Write short applied explanations and self-check for a direct conclusion.</x:v>
       </x:c>
       <x:c r="H11" s="109" t="str">
-        <x:v>Create a simple cashflow-discounting model in Excel.</x:v>
+        <x:v>Build a one-page summary of key distinctions and common command words.</x:v>
       </x:c>
       <x:c r="I11" s="109" t="n">
-        <x:v>20</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="J11" s="109"/>
       <x:c r="K11" s="109"/>
@@ -2965,19 +2965,19 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="D12" s="109" t="str">
-        <x:v>Equation of value and loans</x:v>
+        <x:v>Business ownership and taxation</x:v>
       </x:c>
       <x:c r="E12" s="109" t="str">
-        <x:v>Cashflow valuation, loans, outstanding balances, bonds and yield</x:v>
+        <x:v>Business forms, ownership, tax and corporate structure</x:v>
       </x:c>
       <x:c r="F12" s="109" t="str">
-        <x:v>Draw every cashflow timeline before calculating and practise two methods for loan questions.</x:v>
+        <x:v>Compare each legal form by ownership, risk, capital and control.</x:v>
       </x:c>
       <x:c r="G12" s="109" t="str">
-        <x:v>Complete mixed loan and bond questions under time pressure.</x:v>
+        <x:v>Complete scenario questions requiring a justified recommendation.</x:v>
       </x:c>
       <x:c r="H12" s="109" t="str">
-        <x:v>Build a loan schedule with a rate input and balance check.</x:v>
+        <x:v>Use a simple table to compare tax or cashflow implications.</x:v>
       </x:c>
       <x:c r="I12" s="109" t="n">
         <x:v>18</x:v>
@@ -2996,19 +2996,19 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="D13" s="109" t="str">
-        <x:v>Annuities and duration + Single-life models</x:v>
+        <x:v>Raising finance + Accounts foundations</x:v>
       </x:c>
       <x:c r="E13" s="109" t="str">
-        <x:v>Level and increasing annuities, immunisation and duration concepts; Survival probabilities, life tables, assurance and annuity values</x:v>
+        <x:v>Long and short-term finance, share issues, debt, leasing and working capital; Statement of profit or loss, financial position and cash flows</x:v>
       </x:c>
       <x:c r="F13" s="109" t="str">
-        <x:v>Cover both blocks deliberately: Create a formula map and a list of common timing traps. Then Convert symbols to a timeline and annotate the contingent payment condition.</x:v>
+        <x:v>Cover both blocks deliberately: Create a finance-source comparison: cost, risk, control, flexibility and timing. Then Reconstruct the three statements from a blank template.</x:v>
       </x:c>
       <x:c r="G13" s="109" t="str">
-        <x:v>Prioritise mixed practice across both blocks: Attempt a timed mixed interest-rate set. Then Practise life-contingency questions and rewrite any weak setup.</x:v>
+        <x:v>Prioritise mixed practice across both blocks: Complete finance-choice questions with a stated recommendation. Then Complete an accounts-building question and reconcile every total.</x:v>
       </x:c>
       <x:c r="H13" s="109" t="str">
-        <x:v>Applied practice: Use Excel to compare present values under alternative interest-rate scenarios. Then Calculate life annuity values from a supplied table.</x:v>
+        <x:v>Applied practice: Calculate a lease or short-term financing comparison. Then Create an accounts template with balance checks.</x:v>
       </x:c>
       <x:c r="I13" s="109" t="n">
         <x:v>38</x:v>
@@ -3027,19 +3027,19 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="D14" s="109" t="str">
-        <x:v>Multiple lives and decrements</x:v>
+        <x:v>Accounts construction and groups</x:v>
       </x:c>
       <x:c r="E14" s="109" t="str">
-        <x:v>Joint-life, last-survivor, multiple-decrement and select models</x:v>
+        <x:v>Adjustments, group accounts, insurance and bank accounts</x:v>
       </x:c>
       <x:c r="F14" s="109" t="str">
-        <x:v>Write a decision tree for the status and payment trigger.</x:v>
+        <x:v>Write an adjustment checklist before starting any construction question.</x:v>
       </x:c>
       <x:c r="G14" s="109" t="str">
-        <x:v>Attempt a longer multi-part question and audit the notation.</x:v>
+        <x:v>Attempt a longer multi-part construction question.</x:v>
       </x:c>
       <x:c r="H14" s="109" t="str">
-        <x:v>Model decrement probabilities and test that probabilities reconcile.</x:v>
+        <x:v>Use a spreadsheet to separate adjustments from final statements.</x:v>
       </x:c>
       <x:c r="I14" s="109" t="n">
         <x:v>20</x:v>
@@ -3058,19 +3058,19 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="D15" s="109" t="str">
-        <x:v>Pricing and reserving</x:v>
+        <x:v>Interpreting accounts</x:v>
       </x:c>
       <x:c r="E15" s="109" t="str">
-        <x:v>Net premiums, gross premiums, prospective and retrospective reserves</x:v>
+        <x:v>Ratios, trends, limitations and investor analysis</x:v>
       </x:c>
       <x:c r="F15" s="109" t="str">
-        <x:v>For each formula, state what is being valued, at what time and on what basis.</x:v>
+        <x:v>Use a claim-evidence-conclusion structure for every interpretation paragraph.</x:v>
       </x:c>
       <x:c r="G15" s="109" t="str">
-        <x:v>Complete premium and reserve questions to a strict time budget.</x:v>
+        <x:v>Complete a ratio question, then improve the quality of the narrative answer.</x:v>
       </x:c>
       <x:c r="H15" s="109" t="str">
-        <x:v>Build a reserve roll-forward and investigate each movement.</x:v>
+        <x:v>Calculate and graph a ratio trend from a small data table.</x:v>
       </x:c>
       <x:c r="I15" s="109" t="n">
         <x:v>18</x:v>
@@ -3089,22 +3089,22 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="D16" s="109" t="str">
-        <x:v>Integrated exam practice + Mock and consolidation</x:v>
+        <x:v>Capital structure and growth + Project appraisal and mock</x:v>
       </x:c>
       <x:c r="E16" s="109" t="str">
-        <x:v>Mixed CM1 applications, answer structure and weak-area repair; Whole syllabus, timed practice and final weak-area repair</x:v>
+        <x:v>Derivatives, restructuring, WACC, dividend policy and acquisition; NPV, IRR, risk, capital projects and whole-syllabus consolidation</x:v>
       </x:c>
       <x:c r="F16" s="109" t="str">
-        <x:v>Cover both blocks deliberately: Choose three recurring error themes and revisit them before comfortable topics. Then Create a final formula and notation sheet from memory, then correct it.</x:v>
+        <x:v>Cover both blocks deliberately: Create a decision tree for financing and restructuring recommendations. Then Prepare an investment-appraisal checklist and a final error list.</x:v>
       </x:c>
       <x:c r="G16" s="109" t="str">
-        <x:v>Prioritise mixed practice across both blocks: Complete a substantial timed Paper A-style set and self-mark your method. Then Sit a full mock or equivalent timed set, then separate marking from error correction.</x:v>
+        <x:v>Prioritise mixed practice across both blocks: Complete applied finance questions including a WACC calculation. Then Complete a timed mock or equivalent mixed set, then redraft weak written answers.</x:v>
       </x:c>
       <x:c r="H16" s="109" t="str">
-        <x:v>Applied practice: Complete a timed Excel challenge and check formulas independently. Then Rebuild the weakest modelling task from a blank workbook.</x:v>
+        <x:v>Applied practice: Build a WACC sensitivity table. Then Build an NPV model and test a key sensitivity.</x:v>
       </x:c>
       <x:c r="I16" s="109" t="n">
-        <x:v>55</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="J16" s="109"/>
       <x:c r="K16" s="109"/>
@@ -3120,22 +3120,22 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="109" t="str">
-        <x:v>Theory of interest rates</x:v>
+        <x:v>Governance and objectives</x:v>
       </x:c>
       <x:c r="E17" s="109" t="str">
-        <x:v>Rate conversions, discount functions, force of interest and term structures</x:v>
+        <x:v>Corporate governance, ethics, stakeholders and shareholder wealth</x:v>
       </x:c>
       <x:c r="F17" s="109" t="str">
-        <x:v>Build a one-page rate-conversion sheet and derive each relationship once.</x:v>
+        <x:v>Create a stakeholder-conflict grid and a governance answer plan.</x:v>
       </x:c>
       <x:c r="G17" s="109" t="str">
-        <x:v>Complete short calculations and mark units and timing explicitly.</x:v>
+        <x:v>Write short applied explanations and self-check for a direct conclusion.</x:v>
       </x:c>
       <x:c r="H17" s="109" t="str">
-        <x:v>Create a simple cashflow-discounting model in Excel.</x:v>
+        <x:v>Build a one-page summary of key distinctions and common command words.</x:v>
       </x:c>
       <x:c r="I17" s="109" t="n">
-        <x:v>20</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="J17" s="109"/>
       <x:c r="K17" s="109"/>
@@ -3151,19 +3151,19 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="D18" s="109" t="str">
-        <x:v>Equation of value and loans</x:v>
+        <x:v>Business ownership and taxation</x:v>
       </x:c>
       <x:c r="E18" s="109" t="str">
-        <x:v>Cashflow valuation, loans, outstanding balances, bonds and yield</x:v>
+        <x:v>Business forms, ownership, tax and corporate structure</x:v>
       </x:c>
       <x:c r="F18" s="109" t="str">
-        <x:v>Draw every cashflow timeline before calculating and practise two methods for loan questions.</x:v>
+        <x:v>Compare each legal form by ownership, risk, capital and control.</x:v>
       </x:c>
       <x:c r="G18" s="109" t="str">
-        <x:v>Complete mixed loan and bond questions under time pressure.</x:v>
+        <x:v>Complete scenario questions requiring a justified recommendation.</x:v>
       </x:c>
       <x:c r="H18" s="109" t="str">
-        <x:v>Build a loan schedule with a rate input and balance check.</x:v>
+        <x:v>Use a simple table to compare tax or cashflow implications.</x:v>
       </x:c>
       <x:c r="I18" s="109" t="n">
         <x:v>18</x:v>
@@ -3182,22 +3182,22 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="D19" s="109" t="str">
-        <x:v>Annuities and duration</x:v>
+        <x:v>Raising finance</x:v>
       </x:c>
       <x:c r="E19" s="109" t="str">
-        <x:v>Level and increasing annuities, immunisation and duration concepts</x:v>
+        <x:v>Long and short-term finance, share issues, debt, leasing and working capital</x:v>
       </x:c>
       <x:c r="F19" s="109" t="str">
-        <x:v>Create a formula map and a list of common timing traps.</x:v>
+        <x:v>Create a finance-source comparison: cost, risk, control, flexibility and timing.</x:v>
       </x:c>
       <x:c r="G19" s="109" t="str">
-        <x:v>Attempt a timed mixed interest-rate set.</x:v>
+        <x:v>Complete finance-choice questions with a stated recommendation.</x:v>
       </x:c>
       <x:c r="H19" s="109" t="str">
-        <x:v>Use Excel to compare present values under alternative interest-rate scenarios.</x:v>
+        <x:v>Calculate a lease or short-term financing comparison.</x:v>
       </x:c>
       <x:c r="I19" s="109" t="n">
-        <x:v>18</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="J19" s="109"/>
       <x:c r="K19" s="109"/>
@@ -3213,22 +3213,22 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="D20" s="109" t="str">
-        <x:v>Single-life models</x:v>
+        <x:v>Accounts foundations</x:v>
       </x:c>
       <x:c r="E20" s="109" t="str">
-        <x:v>Survival probabilities, life tables, assurance and annuity values</x:v>
+        <x:v>Statement of profit or loss, financial position and cash flows</x:v>
       </x:c>
       <x:c r="F20" s="109" t="str">
-        <x:v>Convert symbols to a timeline and annotate the contingent payment condition.</x:v>
+        <x:v>Reconstruct the three statements from a blank template.</x:v>
       </x:c>
       <x:c r="G20" s="109" t="str">
-        <x:v>Practise life-contingency questions and rewrite any weak setup.</x:v>
+        <x:v>Complete an accounts-building question and reconcile every total.</x:v>
       </x:c>
       <x:c r="H20" s="109" t="str">
-        <x:v>Calculate life annuity values from a supplied table.</x:v>
+        <x:v>Create an accounts template with balance checks.</x:v>
       </x:c>
       <x:c r="I20" s="109" t="n">
-        <x:v>20</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="J20" s="109"/>
       <x:c r="K20" s="109"/>
@@ -3244,19 +3244,19 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="D21" s="109" t="str">
-        <x:v>Multiple lives and decrements</x:v>
+        <x:v>Accounts construction and groups</x:v>
       </x:c>
       <x:c r="E21" s="109" t="str">
-        <x:v>Joint-life, last-survivor, multiple-decrement and select models</x:v>
+        <x:v>Adjustments, group accounts, insurance and bank accounts</x:v>
       </x:c>
       <x:c r="F21" s="109" t="str">
-        <x:v>Write a decision tree for the status and payment trigger.</x:v>
+        <x:v>Write an adjustment checklist before starting any construction question.</x:v>
       </x:c>
       <x:c r="G21" s="109" t="str">
-        <x:v>Attempt a longer multi-part question and audit the notation.</x:v>
+        <x:v>Attempt a longer multi-part construction question.</x:v>
       </x:c>
       <x:c r="H21" s="109" t="str">
-        <x:v>Model decrement probabilities and test that probabilities reconcile.</x:v>
+        <x:v>Use a spreadsheet to separate adjustments from final statements.</x:v>
       </x:c>
       <x:c r="I21" s="109" t="n">
         <x:v>20</x:v>
@@ -3275,19 +3275,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="D22" s="109" t="str">
-        <x:v>Pricing and reserving</x:v>
+        <x:v>Interpreting accounts</x:v>
       </x:c>
       <x:c r="E22" s="109" t="str">
-        <x:v>Net premiums, gross premiums, prospective and retrospective reserves</x:v>
+        <x:v>Ratios, trends, limitations and investor analysis</x:v>
       </x:c>
       <x:c r="F22" s="109" t="str">
-        <x:v>For each formula, state what is being valued, at what time and on what basis.</x:v>
+        <x:v>Use a claim-evidence-conclusion structure for every interpretation paragraph.</x:v>
       </x:c>
       <x:c r="G22" s="109" t="str">
-        <x:v>Complete premium and reserve questions to a strict time budget.</x:v>
+        <x:v>Complete a ratio question, then improve the quality of the narrative answer.</x:v>
       </x:c>
       <x:c r="H22" s="109" t="str">
-        <x:v>Build a reserve roll-forward and investigate each movement.</x:v>
+        <x:v>Calculate and graph a ratio trend from a small data table.</x:v>
       </x:c>
       <x:c r="I22" s="109" t="n">
         <x:v>18</x:v>
@@ -3306,22 +3306,22 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D23" s="109" t="str">
-        <x:v>Integrated exam practice + Mock and consolidation</x:v>
+        <x:v>Capital structure and growth + Project appraisal and mock</x:v>
       </x:c>
       <x:c r="E23" s="109" t="str">
-        <x:v>Mixed CM1 applications, answer structure and weak-area repair; Whole syllabus, timed practice and final weak-area repair</x:v>
+        <x:v>Derivatives, restructuring, WACC, dividend policy and acquisition; NPV, IRR, risk, capital projects and whole-syllabus consolidation</x:v>
       </x:c>
       <x:c r="F23" s="109" t="str">
-        <x:v>Cover both blocks deliberately: Choose three recurring error themes and revisit them before comfortable topics. Then Create a final formula and notation sheet from memory, then correct it.</x:v>
+        <x:v>Cover both blocks deliberately: Create a decision tree for financing and restructuring recommendations. Then Prepare an investment-appraisal checklist and a final error list.</x:v>
       </x:c>
       <x:c r="G23" s="109" t="str">
-        <x:v>Prioritise mixed practice across both blocks: Complete a substantial timed Paper A-style set and self-mark your method. Then Sit a full mock or equivalent timed set, then separate marking from error correction.</x:v>
+        <x:v>Prioritise mixed practice across both blocks: Complete applied finance questions including a WACC calculation. Then Complete a timed mock or equivalent mixed set, then redraft weak written answers.</x:v>
       </x:c>
       <x:c r="H23" s="109" t="str">
-        <x:v>Applied practice: Complete a timed Excel challenge and check formulas independently. Then Rebuild the weakest modelling task from a blank workbook.</x:v>
+        <x:v>Applied practice: Build a WACC sensitivity table. Then Build an NPV model and test a key sensitivity.</x:v>
       </x:c>
       <x:c r="I23" s="109" t="n">
-        <x:v>55</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="J23" s="109"/>
       <x:c r="K23" s="109"/>
@@ -3337,22 +3337,22 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="D24" s="109" t="str">
-        <x:v>Theory of interest rates</x:v>
+        <x:v>Governance and objectives</x:v>
       </x:c>
       <x:c r="E24" s="109" t="str">
-        <x:v>Rate conversions, discount functions, force of interest and term structures</x:v>
+        <x:v>Corporate governance, ethics, stakeholders and shareholder wealth</x:v>
       </x:c>
       <x:c r="F24" s="109" t="str">
-        <x:v>Build a one-page rate-conversion sheet and derive each relationship once.</x:v>
+        <x:v>Create a stakeholder-conflict grid and a governance answer plan.</x:v>
       </x:c>
       <x:c r="G24" s="109" t="str">
-        <x:v>Complete short calculations and mark units and timing explicitly.</x:v>
+        <x:v>Write short applied explanations and self-check for a direct conclusion.</x:v>
       </x:c>
       <x:c r="H24" s="109" t="str">
-        <x:v>Create a simple cashflow-discounting model in Excel.</x:v>
+        <x:v>Build a one-page summary of key distinctions and common command words.</x:v>
       </x:c>
       <x:c r="I24" s="109" t="n">
-        <x:v>20</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="J24" s="109"/>
       <x:c r="K24" s="109"/>
@@ -3368,19 +3368,19 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="D25" s="109" t="str">
-        <x:v>Equation of value and loans</x:v>
+        <x:v>Business ownership and taxation</x:v>
       </x:c>
       <x:c r="E25" s="109" t="str">
-        <x:v>Cashflow valuation, loans, outstanding balances, bonds and yield</x:v>
+        <x:v>Business forms, ownership, tax and corporate structure</x:v>
       </x:c>
       <x:c r="F25" s="109" t="str">
-        <x:v>Draw every cashflow timeline before calculating and practise two methods for loan questions.</x:v>
+        <x:v>Compare each legal form by ownership, risk, capital and control.</x:v>
       </x:c>
       <x:c r="G25" s="109" t="str">
-        <x:v>Complete mixed loan and bond questions under time pressure.</x:v>
+        <x:v>Complete scenario questions requiring a justified recommendation.</x:v>
       </x:c>
       <x:c r="H25" s="109" t="str">
-        <x:v>Build a loan schedule with a rate input and balance check.</x:v>
+        <x:v>Use a simple table to compare tax or cashflow implications.</x:v>
       </x:c>
       <x:c r="I25" s="109" t="n">
         <x:v>18</x:v>
@@ -3399,22 +3399,22 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="D26" s="109" t="str">
-        <x:v>Annuities and duration</x:v>
+        <x:v>Raising finance</x:v>
       </x:c>
       <x:c r="E26" s="109" t="str">
-        <x:v>Level and increasing annuities, immunisation and duration concepts</x:v>
+        <x:v>Long and short-term finance, share issues, debt, leasing and working capital</x:v>
       </x:c>
       <x:c r="F26" s="109" t="str">
-        <x:v>Create a formula map and a list of common timing traps.</x:v>
+        <x:v>Create a finance-source comparison: cost, risk, control, flexibility and timing.</x:v>
       </x:c>
       <x:c r="G26" s="109" t="str">
-        <x:v>Attempt a timed mixed interest-rate set.</x:v>
+        <x:v>Complete finance-choice questions with a stated recommendation.</x:v>
       </x:c>
       <x:c r="H26" s="109" t="str">
-        <x:v>Use Excel to compare present values under alternative interest-rate scenarios.</x:v>
+        <x:v>Calculate a lease or short-term financing comparison.</x:v>
       </x:c>
       <x:c r="I26" s="109" t="n">
-        <x:v>18</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="J26" s="109"/>
       <x:c r="K26" s="109"/>
@@ -3430,22 +3430,22 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="D27" s="109" t="str">
-        <x:v>Single-life models</x:v>
+        <x:v>Accounts foundations</x:v>
       </x:c>
       <x:c r="E27" s="109" t="str">
-        <x:v>Survival probabilities, life tables, assurance and annuity values</x:v>
+        <x:v>Statement of profit or loss, financial position and cash flows</x:v>
       </x:c>
       <x:c r="F27" s="109" t="str">
-        <x:v>Convert symbols to a timeline and annotate the contingent payment condition.</x:v>
+        <x:v>Reconstruct the three statements from a blank template.</x:v>
       </x:c>
       <x:c r="G27" s="109" t="str">
-        <x:v>Practise life-contingency questions and rewrite any weak setup.</x:v>
+        <x:v>Complete an accounts-building question and reconcile every total.</x:v>
       </x:c>
       <x:c r="H27" s="109" t="str">
-        <x:v>Calculate life annuity values from a supplied table.</x:v>
+        <x:v>Create an accounts template with balance checks.</x:v>
       </x:c>
       <x:c r="I27" s="109" t="n">
-        <x:v>20</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="J27" s="109"/>
       <x:c r="K27" s="109"/>
@@ -3461,19 +3461,19 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="D28" s="109" t="str">
-        <x:v>Multiple lives and decrements</x:v>
+        <x:v>Accounts construction and groups</x:v>
       </x:c>
       <x:c r="E28" s="109" t="str">
-        <x:v>Joint-life, last-survivor, multiple-decrement and select models</x:v>
+        <x:v>Adjustments, group accounts, insurance and bank accounts</x:v>
       </x:c>
       <x:c r="F28" s="109" t="str">
-        <x:v>Write a decision tree for the status and payment trigger.</x:v>
+        <x:v>Write an adjustment checklist before starting any construction question.</x:v>
       </x:c>
       <x:c r="G28" s="109" t="str">
-        <x:v>Attempt a longer multi-part question and audit the notation.</x:v>
+        <x:v>Attempt a longer multi-part construction question.</x:v>
       </x:c>
       <x:c r="H28" s="109" t="str">
-        <x:v>Model decrement probabilities and test that probabilities reconcile.</x:v>
+        <x:v>Use a spreadsheet to separate adjustments from final statements.</x:v>
       </x:c>
       <x:c r="I28" s="109" t="n">
         <x:v>20</x:v>
@@ -3492,19 +3492,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="D29" s="109" t="str">
-        <x:v>Pricing and reserving</x:v>
+        <x:v>Interpreting accounts</x:v>
       </x:c>
       <x:c r="E29" s="109" t="str">
-        <x:v>Net premiums, gross premiums, prospective and retrospective reserves</x:v>
+        <x:v>Ratios, trends, limitations and investor analysis</x:v>
       </x:c>
       <x:c r="F29" s="109" t="str">
-        <x:v>For each formula, state what is being valued, at what time and on what basis.</x:v>
+        <x:v>Use a claim-evidence-conclusion structure for every interpretation paragraph.</x:v>
       </x:c>
       <x:c r="G29" s="109" t="str">
-        <x:v>Complete premium and reserve questions to a strict time budget.</x:v>
+        <x:v>Complete a ratio question, then improve the quality of the narrative answer.</x:v>
       </x:c>
       <x:c r="H29" s="109" t="str">
-        <x:v>Build a reserve roll-forward and investigate each movement.</x:v>
+        <x:v>Calculate and graph a ratio trend from a small data table.</x:v>
       </x:c>
       <x:c r="I29" s="109" t="n">
         <x:v>18</x:v>
@@ -3523,22 +3523,22 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D30" s="109" t="str">
-        <x:v>Integrated exam practice</x:v>
+        <x:v>Capital structure and growth</x:v>
       </x:c>
       <x:c r="E30" s="109" t="str">
-        <x:v>Mixed CM1 applications, answer structure and weak-area repair</x:v>
+        <x:v>Derivatives, restructuring, WACC, dividend policy and acquisition</x:v>
       </x:c>
       <x:c r="F30" s="109" t="str">
-        <x:v>Choose three recurring error themes and revisit them before comfortable topics.</x:v>
+        <x:v>Create a decision tree for financing and restructuring recommendations.</x:v>
       </x:c>
       <x:c r="G30" s="109" t="str">
-        <x:v>Complete a substantial timed Paper A-style set and self-mark your method.</x:v>
+        <x:v>Complete applied finance questions including a WACC calculation.</x:v>
       </x:c>
       <x:c r="H30" s="109" t="str">
-        <x:v>Complete a timed Excel challenge and check formulas independently.</x:v>
+        <x:v>Build a WACC sensitivity table.</x:v>
       </x:c>
       <x:c r="I30" s="109" t="n">
-        <x:v>25</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="J30" s="109"/>
       <x:c r="K30" s="109"/>
@@ -3554,22 +3554,22 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D31" s="109" t="str">
-        <x:v>Mock and consolidation</x:v>
+        <x:v>Project appraisal and mock</x:v>
       </x:c>
       <x:c r="E31" s="109" t="str">
-        <x:v>Whole syllabus, timed practice and final weak-area repair</x:v>
+        <x:v>NPV, IRR, risk, capital projects and whole-syllabus consolidation</x:v>
       </x:c>
       <x:c r="F31" s="109" t="str">
-        <x:v>Create a final formula and notation sheet from memory, then correct it.</x:v>
+        <x:v>Prepare an investment-appraisal checklist and a final error list.</x:v>
       </x:c>
       <x:c r="G31" s="109" t="str">
-        <x:v>Sit a full mock or equivalent timed set, then separate marking from error correction.</x:v>
+        <x:v>Complete a timed mock or equivalent mixed set, then redraft weak written answers.</x:v>
       </x:c>
       <x:c r="H31" s="109" t="str">
-        <x:v>Rebuild the weakest modelling task from a blank workbook.</x:v>
+        <x:v>Build an NPV model and test a key sensitivity.</x:v>
       </x:c>
       <x:c r="I31" s="109" t="n">
-        <x:v>30</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="J31" s="109"/>
       <x:c r="K31" s="109"/>
@@ -3585,22 +3585,22 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="D32" s="109" t="str">
-        <x:v>Theory of interest rates</x:v>
+        <x:v>Governance and objectives</x:v>
       </x:c>
       <x:c r="E32" s="109" t="str">
-        <x:v>Rate conversions, discount functions, force of interest and term structures</x:v>
+        <x:v>Corporate governance, ethics, stakeholders and shareholder wealth</x:v>
       </x:c>
       <x:c r="F32" s="109" t="str">
-        <x:v>Build a one-page rate-conversion sheet and derive each relationship once.</x:v>
+        <x:v>Create a stakeholder-conflict grid and a governance answer plan.</x:v>
       </x:c>
       <x:c r="G32" s="109" t="str">
-        <x:v>Complete short calculations and mark units and timing explicitly.</x:v>
+        <x:v>Write short applied explanations and self-check for a direct conclusion.</x:v>
       </x:c>
       <x:c r="H32" s="109" t="str">
-        <x:v>Create a simple cashflow-discounting model in Excel.</x:v>
+        <x:v>Build a one-page summary of key distinctions and common command words.</x:v>
       </x:c>
       <x:c r="I32" s="109" t="n">
-        <x:v>10</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="J32" s="109"/>
       <x:c r="K32" s="109"/>
@@ -3616,13 +3616,13 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="D33" s="109" t="str">
-        <x:v>Theory of interest rates</x:v>
+        <x:v>Governance and objectives</x:v>
       </x:c>
       <x:c r="E33" s="109" t="str">
-        <x:v>Rate conversions, discount functions, force of interest and term structures</x:v>
+        <x:v>Corporate governance, ethics, stakeholders and shareholder wealth</x:v>
       </x:c>
       <x:c r="F33" s="109" t="str">
-        <x:v>Revisit theory of interest rates from memory, then target the weakest sub-area.</x:v>
+        <x:v>Revisit governance and objectives from memory, then target the weakest sub-area.</x:v>
       </x:c>
       <x:c r="G33" s="109" t="str">
         <x:v>Redo open errors first, then complete another timed mixed set without relying on notes.</x:v>
@@ -3631,7 +3631,7 @@
         <x:v>Repeat the applied task from a blank file or extend it with an independent check or sensitivity.</x:v>
       </x:c>
       <x:c r="I33" s="109" t="n">
-        <x:v>10</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="J33" s="109"/>
       <x:c r="K33" s="109"/>
@@ -3647,19 +3647,19 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="D34" s="109" t="str">
-        <x:v>Equation of value and loans</x:v>
+        <x:v>Business ownership and taxation</x:v>
       </x:c>
       <x:c r="E34" s="109" t="str">
-        <x:v>Cashflow valuation, loans, outstanding balances, bonds and yield</x:v>
+        <x:v>Business forms, ownership, tax and corporate structure</x:v>
       </x:c>
       <x:c r="F34" s="109" t="str">
-        <x:v>Draw every cashflow timeline before calculating and practise two methods for loan questions.</x:v>
+        <x:v>Compare each legal form by ownership, risk, capital and control.</x:v>
       </x:c>
       <x:c r="G34" s="109" t="str">
-        <x:v>Complete mixed loan and bond questions under time pressure.</x:v>
+        <x:v>Complete scenario questions requiring a justified recommendation.</x:v>
       </x:c>
       <x:c r="H34" s="109" t="str">
-        <x:v>Build a loan schedule with a rate input and balance check.</x:v>
+        <x:v>Use a simple table to compare tax or cashflow implications.</x:v>
       </x:c>
       <x:c r="I34" s="109" t="n">
         <x:v>18</x:v>
@@ -3678,22 +3678,22 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="D35" s="109" t="str">
-        <x:v>Annuities and duration</x:v>
+        <x:v>Raising finance</x:v>
       </x:c>
       <x:c r="E35" s="109" t="str">
-        <x:v>Level and increasing annuities, immunisation and duration concepts</x:v>
+        <x:v>Long and short-term finance, share issues, debt, leasing and working capital</x:v>
       </x:c>
       <x:c r="F35" s="109" t="str">
-        <x:v>Create a formula map and a list of common timing traps.</x:v>
+        <x:v>Create a finance-source comparison: cost, risk, control, flexibility and timing.</x:v>
       </x:c>
       <x:c r="G35" s="109" t="str">
-        <x:v>Attempt a timed mixed interest-rate set.</x:v>
+        <x:v>Complete finance-choice questions with a stated recommendation.</x:v>
       </x:c>
       <x:c r="H35" s="109" t="str">
-        <x:v>Use Excel to compare present values under alternative interest-rate scenarios.</x:v>
+        <x:v>Calculate a lease or short-term financing comparison.</x:v>
       </x:c>
       <x:c r="I35" s="109" t="n">
-        <x:v>18</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="J35" s="109"/>
       <x:c r="K35" s="109"/>
@@ -3709,22 +3709,22 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="D36" s="109" t="str">
-        <x:v>Single-life models</x:v>
+        <x:v>Accounts foundations</x:v>
       </x:c>
       <x:c r="E36" s="109" t="str">
-        <x:v>Survival probabilities, life tables, assurance and annuity values</x:v>
+        <x:v>Statement of profit or loss, financial position and cash flows</x:v>
       </x:c>
       <x:c r="F36" s="109" t="str">
-        <x:v>Convert symbols to a timeline and annotate the contingent payment condition.</x:v>
+        <x:v>Reconstruct the three statements from a blank template.</x:v>
       </x:c>
       <x:c r="G36" s="109" t="str">
-        <x:v>Practise life-contingency questions and rewrite any weak setup.</x:v>
+        <x:v>Complete an accounts-building question and reconcile every total.</x:v>
       </x:c>
       <x:c r="H36" s="109" t="str">
-        <x:v>Calculate life annuity values from a supplied table.</x:v>
+        <x:v>Create an accounts template with balance checks.</x:v>
       </x:c>
       <x:c r="I36" s="109" t="n">
-        <x:v>20</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="J36" s="109"/>
       <x:c r="K36" s="109"/>
@@ -3740,19 +3740,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="D37" s="109" t="str">
-        <x:v>Multiple lives and decrements</x:v>
+        <x:v>Accounts construction and groups</x:v>
       </x:c>
       <x:c r="E37" s="109" t="str">
-        <x:v>Joint-life, last-survivor, multiple-decrement and select models</x:v>
+        <x:v>Adjustments, group accounts, insurance and bank accounts</x:v>
       </x:c>
       <x:c r="F37" s="109" t="str">
-        <x:v>Write a decision tree for the status and payment trigger.</x:v>
+        <x:v>Write an adjustment checklist before starting any construction question.</x:v>
       </x:c>
       <x:c r="G37" s="109" t="str">
-        <x:v>Attempt a longer multi-part question and audit the notation.</x:v>
+        <x:v>Attempt a longer multi-part construction question.</x:v>
       </x:c>
       <x:c r="H37" s="109" t="str">
-        <x:v>Model decrement probabilities and test that probabilities reconcile.</x:v>
+        <x:v>Use a spreadsheet to separate adjustments from final statements.</x:v>
       </x:c>
       <x:c r="I37" s="109" t="n">
         <x:v>20</x:v>
@@ -3771,19 +3771,19 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D38" s="109" t="str">
-        <x:v>Pricing and reserving</x:v>
+        <x:v>Interpreting accounts</x:v>
       </x:c>
       <x:c r="E38" s="109" t="str">
-        <x:v>Net premiums, gross premiums, prospective and retrospective reserves</x:v>
+        <x:v>Ratios, trends, limitations and investor analysis</x:v>
       </x:c>
       <x:c r="F38" s="109" t="str">
-        <x:v>For each formula, state what is being valued, at what time and on what basis.</x:v>
+        <x:v>Use a claim-evidence-conclusion structure for every interpretation paragraph.</x:v>
       </x:c>
       <x:c r="G38" s="109" t="str">
-        <x:v>Complete premium and reserve questions to a strict time budget.</x:v>
+        <x:v>Complete a ratio question, then improve the quality of the narrative answer.</x:v>
       </x:c>
       <x:c r="H38" s="109" t="str">
-        <x:v>Build a reserve roll-forward and investigate each movement.</x:v>
+        <x:v>Calculate and graph a ratio trend from a small data table.</x:v>
       </x:c>
       <x:c r="I38" s="109" t="n">
         <x:v>18</x:v>
@@ -3802,22 +3802,22 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D39" s="109" t="str">
-        <x:v>Integrated exam practice</x:v>
+        <x:v>Capital structure and growth</x:v>
       </x:c>
       <x:c r="E39" s="109" t="str">
-        <x:v>Mixed CM1 applications, answer structure and weak-area repair</x:v>
+        <x:v>Derivatives, restructuring, WACC, dividend policy and acquisition</x:v>
       </x:c>
       <x:c r="F39" s="109" t="str">
-        <x:v>Choose three recurring error themes and revisit them before comfortable topics.</x:v>
+        <x:v>Create a decision tree for financing and restructuring recommendations.</x:v>
       </x:c>
       <x:c r="G39" s="109" t="str">
-        <x:v>Complete a substantial timed Paper A-style set and self-mark your method.</x:v>
+        <x:v>Complete applied finance questions including a WACC calculation.</x:v>
       </x:c>
       <x:c r="H39" s="109" t="str">
-        <x:v>Complete a timed Excel challenge and check formulas independently.</x:v>
+        <x:v>Build a WACC sensitivity table.</x:v>
       </x:c>
       <x:c r="I39" s="109" t="n">
-        <x:v>25</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="J39" s="109"/>
       <x:c r="K39" s="109"/>
@@ -3833,22 +3833,22 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D40" s="109" t="str">
-        <x:v>Mock and consolidation</x:v>
+        <x:v>Project appraisal and mock</x:v>
       </x:c>
       <x:c r="E40" s="109" t="str">
-        <x:v>Whole syllabus, timed practice and final weak-area repair</x:v>
+        <x:v>NPV, IRR, risk, capital projects and whole-syllabus consolidation</x:v>
       </x:c>
       <x:c r="F40" s="109" t="str">
-        <x:v>Create a final formula and notation sheet from memory, then correct it.</x:v>
+        <x:v>Prepare an investment-appraisal checklist and a final error list.</x:v>
       </x:c>
       <x:c r="G40" s="109" t="str">
-        <x:v>Sit a full mock or equivalent timed set, then separate marking from error correction.</x:v>
+        <x:v>Complete a timed mock or equivalent mixed set, then redraft weak written answers.</x:v>
       </x:c>
       <x:c r="H40" s="109" t="str">
-        <x:v>Rebuild the weakest modelling task from a blank workbook.</x:v>
+        <x:v>Build an NPV model and test a key sensitivity.</x:v>
       </x:c>
       <x:c r="I40" s="109" t="n">
-        <x:v>30</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="J40" s="109"/>
       <x:c r="K40" s="109"/>
@@ -3864,22 +3864,22 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="D41" s="109" t="str">
-        <x:v>Theory of interest rates</x:v>
+        <x:v>Governance and objectives</x:v>
       </x:c>
       <x:c r="E41" s="109" t="str">
-        <x:v>Rate conversions, discount functions, force of interest and term structures</x:v>
+        <x:v>Corporate governance, ethics, stakeholders and shareholder wealth</x:v>
       </x:c>
       <x:c r="F41" s="109" t="str">
-        <x:v>Build a one-page rate-conversion sheet and derive each relationship once.</x:v>
+        <x:v>Create a stakeholder-conflict grid and a governance answer plan.</x:v>
       </x:c>
       <x:c r="G41" s="109" t="str">
-        <x:v>Complete short calculations and mark units and timing explicitly.</x:v>
+        <x:v>Write short applied explanations and self-check for a direct conclusion.</x:v>
       </x:c>
       <x:c r="H41" s="109" t="str">
-        <x:v>Create a simple cashflow-discounting model in Excel.</x:v>
+        <x:v>Build a one-page summary of key distinctions and common command words.</x:v>
       </x:c>
       <x:c r="I41" s="109" t="n">
-        <x:v>10</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="J41" s="109"/>
       <x:c r="K41" s="109"/>
@@ -3895,13 +3895,13 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="D42" s="109" t="str">
-        <x:v>Theory of interest rates</x:v>
+        <x:v>Governance and objectives</x:v>
       </x:c>
       <x:c r="E42" s="109" t="str">
-        <x:v>Rate conversions, discount functions, force of interest and term structures</x:v>
+        <x:v>Corporate governance, ethics, stakeholders and shareholder wealth</x:v>
       </x:c>
       <x:c r="F42" s="109" t="str">
-        <x:v>Revisit theory of interest rates from memory, then target the weakest sub-area.</x:v>
+        <x:v>Revisit governance and objectives from memory, then target the weakest sub-area.</x:v>
       </x:c>
       <x:c r="G42" s="109" t="str">
         <x:v>Redo open errors first, then complete another timed mixed set without relying on notes.</x:v>
@@ -3910,7 +3910,7 @@
         <x:v>Repeat the applied task from a blank file or extend it with an independent check or sensitivity.</x:v>
       </x:c>
       <x:c r="I42" s="109" t="n">
-        <x:v>10</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="J42" s="109"/>
       <x:c r="K42" s="109"/>
@@ -3926,19 +3926,19 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="D43" s="109" t="str">
-        <x:v>Equation of value and loans</x:v>
+        <x:v>Business ownership and taxation</x:v>
       </x:c>
       <x:c r="E43" s="109" t="str">
-        <x:v>Cashflow valuation, loans, outstanding balances, bonds and yield</x:v>
+        <x:v>Business forms, ownership, tax and corporate structure</x:v>
       </x:c>
       <x:c r="F43" s="109" t="str">
-        <x:v>Draw every cashflow timeline before calculating and practise two methods for loan questions.</x:v>
+        <x:v>Compare each legal form by ownership, risk, capital and control.</x:v>
       </x:c>
       <x:c r="G43" s="109" t="str">
-        <x:v>Complete mixed loan and bond questions under time pressure.</x:v>
+        <x:v>Complete scenario questions requiring a justified recommendation.</x:v>
       </x:c>
       <x:c r="H43" s="109" t="str">
-        <x:v>Build a loan schedule with a rate input and balance check.</x:v>
+        <x:v>Use a simple table to compare tax or cashflow implications.</x:v>
       </x:c>
       <x:c r="I43" s="109" t="n">
         <x:v>18</x:v>
@@ -3957,22 +3957,22 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="D44" s="109" t="str">
-        <x:v>Annuities and duration</x:v>
+        <x:v>Raising finance</x:v>
       </x:c>
       <x:c r="E44" s="109" t="str">
-        <x:v>Level and increasing annuities, immunisation and duration concepts</x:v>
+        <x:v>Long and short-term finance, share issues, debt, leasing and working capital</x:v>
       </x:c>
       <x:c r="F44" s="109" t="str">
-        <x:v>Create a formula map and a list of common timing traps.</x:v>
+        <x:v>Create a finance-source comparison: cost, risk, control, flexibility and timing.</x:v>
       </x:c>
       <x:c r="G44" s="109" t="str">
-        <x:v>Attempt a timed mixed interest-rate set.</x:v>
+        <x:v>Complete finance-choice questions with a stated recommendation.</x:v>
       </x:c>
       <x:c r="H44" s="109" t="str">
-        <x:v>Use Excel to compare present values under alternative interest-rate scenarios.</x:v>
+        <x:v>Calculate a lease or short-term financing comparison.</x:v>
       </x:c>
       <x:c r="I44" s="109" t="n">
-        <x:v>18</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="J44" s="109"/>
       <x:c r="K44" s="109"/>
@@ -3988,22 +3988,22 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="D45" s="109" t="str">
-        <x:v>Single-life models</x:v>
+        <x:v>Accounts foundations</x:v>
       </x:c>
       <x:c r="E45" s="109" t="str">
-        <x:v>Survival probabilities, life tables, assurance and annuity values</x:v>
+        <x:v>Statement of profit or loss, financial position and cash flows</x:v>
       </x:c>
       <x:c r="F45" s="109" t="str">
-        <x:v>Convert symbols to a timeline and annotate the contingent payment condition.</x:v>
+        <x:v>Reconstruct the three statements from a blank template.</x:v>
       </x:c>
       <x:c r="G45" s="109" t="str">
-        <x:v>Practise life-contingency questions and rewrite any weak setup.</x:v>
+        <x:v>Complete an accounts-building question and reconcile every total.</x:v>
       </x:c>
       <x:c r="H45" s="109" t="str">
-        <x:v>Calculate life annuity values from a supplied table.</x:v>
+        <x:v>Create an accounts template with balance checks.</x:v>
       </x:c>
       <x:c r="I45" s="109" t="n">
-        <x:v>20</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="J45" s="109"/>
       <x:c r="K45" s="109"/>
@@ -4019,19 +4019,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="D46" s="109" t="str">
-        <x:v>Multiple lives and decrements</x:v>
+        <x:v>Accounts construction and groups</x:v>
       </x:c>
       <x:c r="E46" s="109" t="str">
-        <x:v>Joint-life, last-survivor, multiple-decrement and select models</x:v>
+        <x:v>Adjustments, group accounts, insurance and bank accounts</x:v>
       </x:c>
       <x:c r="F46" s="109" t="str">
-        <x:v>Write a decision tree for the status and payment trigger.</x:v>
+        <x:v>Write an adjustment checklist before starting any construction question.</x:v>
       </x:c>
       <x:c r="G46" s="109" t="str">
-        <x:v>Attempt a longer multi-part question and audit the notation.</x:v>
+        <x:v>Attempt a longer multi-part construction question.</x:v>
       </x:c>
       <x:c r="H46" s="109" t="str">
-        <x:v>Model decrement probabilities and test that probabilities reconcile.</x:v>
+        <x:v>Use a spreadsheet to separate adjustments from final statements.</x:v>
       </x:c>
       <x:c r="I46" s="109" t="n">
         <x:v>10</x:v>
@@ -4050,13 +4050,13 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D47" s="109" t="str">
-        <x:v>Multiple lives and decrements</x:v>
+        <x:v>Accounts construction and groups</x:v>
       </x:c>
       <x:c r="E47" s="109" t="str">
-        <x:v>Joint-life, last-survivor, multiple-decrement and select models</x:v>
+        <x:v>Adjustments, group accounts, insurance and bank accounts</x:v>
       </x:c>
       <x:c r="F47" s="109" t="str">
-        <x:v>Revisit multiple lives and decrements from memory, then target the weakest sub-area.</x:v>
+        <x:v>Revisit accounts construction and groups from memory, then target the weakest sub-area.</x:v>
       </x:c>
       <x:c r="G47" s="109" t="str">
         <x:v>Redo open errors first, then complete another timed mixed set without relying on notes.</x:v>
@@ -4081,19 +4081,19 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D48" s="109" t="str">
-        <x:v>Pricing and reserving</x:v>
+        <x:v>Interpreting accounts</x:v>
       </x:c>
       <x:c r="E48" s="109" t="str">
-        <x:v>Net premiums, gross premiums, prospective and retrospective reserves</x:v>
+        <x:v>Ratios, trends, limitations and investor analysis</x:v>
       </x:c>
       <x:c r="F48" s="109" t="str">
-        <x:v>For each formula, state what is being valued, at what time and on what basis.</x:v>
+        <x:v>Use a claim-evidence-conclusion structure for every interpretation paragraph.</x:v>
       </x:c>
       <x:c r="G48" s="109" t="str">
-        <x:v>Complete premium and reserve questions to a strict time budget.</x:v>
+        <x:v>Complete a ratio question, then improve the quality of the narrative answer.</x:v>
       </x:c>
       <x:c r="H48" s="109" t="str">
-        <x:v>Build a reserve roll-forward and investigate each movement.</x:v>
+        <x:v>Calculate and graph a ratio trend from a small data table.</x:v>
       </x:c>
       <x:c r="I48" s="109" t="n">
         <x:v>18</x:v>
@@ -4112,22 +4112,22 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D49" s="109" t="str">
-        <x:v>Integrated exam practice</x:v>
+        <x:v>Capital structure and growth</x:v>
       </x:c>
       <x:c r="E49" s="109" t="str">
-        <x:v>Mixed CM1 applications, answer structure and weak-area repair</x:v>
+        <x:v>Derivatives, restructuring, WACC, dividend policy and acquisition</x:v>
       </x:c>
       <x:c r="F49" s="109" t="str">
-        <x:v>Choose three recurring error themes and revisit them before comfortable topics.</x:v>
+        <x:v>Create a decision tree for financing and restructuring recommendations.</x:v>
       </x:c>
       <x:c r="G49" s="109" t="str">
-        <x:v>Complete a substantial timed Paper A-style set and self-mark your method.</x:v>
+        <x:v>Complete applied finance questions including a WACC calculation.</x:v>
       </x:c>
       <x:c r="H49" s="109" t="str">
-        <x:v>Complete a timed Excel challenge and check formulas independently.</x:v>
+        <x:v>Build a WACC sensitivity table.</x:v>
       </x:c>
       <x:c r="I49" s="109" t="n">
-        <x:v>25</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="J49" s="109"/>
       <x:c r="K49" s="109"/>
@@ -4143,22 +4143,22 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="D50" s="109" t="str">
-        <x:v>Mock and consolidation</x:v>
+        <x:v>Project appraisal and mock</x:v>
       </x:c>
       <x:c r="E50" s="109" t="str">
-        <x:v>Whole syllabus, timed practice and final weak-area repair</x:v>
+        <x:v>NPV, IRR, risk, capital projects and whole-syllabus consolidation</x:v>
       </x:c>
       <x:c r="F50" s="109" t="str">
-        <x:v>Create a final formula and notation sheet from memory, then correct it.</x:v>
+        <x:v>Prepare an investment-appraisal checklist and a final error list.</x:v>
       </x:c>
       <x:c r="G50" s="109" t="str">
-        <x:v>Sit a full mock or equivalent timed set, then separate marking from error correction.</x:v>
+        <x:v>Complete a timed mock or equivalent mixed set, then redraft weak written answers.</x:v>
       </x:c>
       <x:c r="H50" s="109" t="str">
-        <x:v>Rebuild the weakest modelling task from a blank workbook.</x:v>
+        <x:v>Build an NPV model and test a key sensitivity.</x:v>
       </x:c>
       <x:c r="I50" s="109" t="n">
-        <x:v>30</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="J50" s="109"/>
       <x:c r="K50" s="109"/>
@@ -4174,22 +4174,22 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="D51" s="109" t="str">
-        <x:v>Theory of interest rates</x:v>
+        <x:v>Governance and objectives</x:v>
       </x:c>
       <x:c r="E51" s="109" t="str">
-        <x:v>Rate conversions, discount functions, force of interest and term structures</x:v>
+        <x:v>Corporate governance, ethics, stakeholders and shareholder wealth</x:v>
       </x:c>
       <x:c r="F51" s="109" t="str">
-        <x:v>Build a one-page rate-conversion sheet and derive each relationship once.</x:v>
+        <x:v>Create a stakeholder-conflict grid and a governance answer plan.</x:v>
       </x:c>
       <x:c r="G51" s="109" t="str">
-        <x:v>Complete short calculations and mark units and timing explicitly.</x:v>
+        <x:v>Write short applied explanations and self-check for a direct conclusion.</x:v>
       </x:c>
       <x:c r="H51" s="109" t="str">
-        <x:v>Create a simple cashflow-discounting model in Excel.</x:v>
+        <x:v>Build a one-page summary of key distinctions and common command words.</x:v>
       </x:c>
       <x:c r="I51" s="109" t="n">
-        <x:v>10</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="J51" s="109"/>
       <x:c r="K51" s="109"/>
@@ -4205,13 +4205,13 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="D52" s="109" t="str">
-        <x:v>Theory of interest rates</x:v>
+        <x:v>Governance and objectives</x:v>
       </x:c>
       <x:c r="E52" s="109" t="str">
-        <x:v>Rate conversions, discount functions, force of interest and term structures</x:v>
+        <x:v>Corporate governance, ethics, stakeholders and shareholder wealth</x:v>
       </x:c>
       <x:c r="F52" s="109" t="str">
-        <x:v>Revisit theory of interest rates from memory, then target the weakest sub-area.</x:v>
+        <x:v>Revisit governance and objectives from memory, then target the weakest sub-area.</x:v>
       </x:c>
       <x:c r="G52" s="109" t="str">
         <x:v>Redo open errors first, then complete another timed mixed set without relying on notes.</x:v>
@@ -4220,7 +4220,7 @@
         <x:v>Repeat the applied task from a blank file or extend it with an independent check or sensitivity.</x:v>
       </x:c>
       <x:c r="I52" s="109" t="n">
-        <x:v>10</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="J52" s="109"/>
       <x:c r="K52" s="109"/>
@@ -4236,19 +4236,19 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="D53" s="109" t="str">
-        <x:v>Equation of value and loans</x:v>
+        <x:v>Business ownership and taxation</x:v>
       </x:c>
       <x:c r="E53" s="109" t="str">
-        <x:v>Cashflow valuation, loans, outstanding balances, bonds and yield</x:v>
+        <x:v>Business forms, ownership, tax and corporate structure</x:v>
       </x:c>
       <x:c r="F53" s="109" t="str">
-        <x:v>Draw every cashflow timeline before calculating and practise two methods for loan questions.</x:v>
+        <x:v>Compare each legal form by ownership, risk, capital and control.</x:v>
       </x:c>
       <x:c r="G53" s="109" t="str">
-        <x:v>Complete mixed loan and bond questions under time pressure.</x:v>
+        <x:v>Complete scenario questions requiring a justified recommendation.</x:v>
       </x:c>
       <x:c r="H53" s="109" t="str">
-        <x:v>Build a loan schedule with a rate input and balance check.</x:v>
+        <x:v>Use a simple table to compare tax or cashflow implications.</x:v>
       </x:c>
       <x:c r="I53" s="109" t="n">
         <x:v>18</x:v>
@@ -4267,22 +4267,22 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="D54" s="109" t="str">
-        <x:v>Annuities and duration</x:v>
+        <x:v>Raising finance</x:v>
       </x:c>
       <x:c r="E54" s="109" t="str">
-        <x:v>Level and increasing annuities, immunisation and duration concepts</x:v>
+        <x:v>Long and short-term finance, share issues, debt, leasing and working capital</x:v>
       </x:c>
       <x:c r="F54" s="109" t="str">
-        <x:v>Create a formula map and a list of common timing traps.</x:v>
+        <x:v>Create a finance-source comparison: cost, risk, control, flexibility and timing.</x:v>
       </x:c>
       <x:c r="G54" s="109" t="str">
-        <x:v>Attempt a timed mixed interest-rate set.</x:v>
+        <x:v>Complete finance-choice questions with a stated recommendation.</x:v>
       </x:c>
       <x:c r="H54" s="109" t="str">
-        <x:v>Use Excel to compare present values under alternative interest-rate scenarios.</x:v>
+        <x:v>Calculate a lease or short-term financing comparison.</x:v>
       </x:c>
       <x:c r="I54" s="109" t="n">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="J54" s="109"/>
       <x:c r="K54" s="109"/>
@@ -4298,13 +4298,13 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="D55" s="109" t="str">
-        <x:v>Annuities and duration</x:v>
+        <x:v>Raising finance</x:v>
       </x:c>
       <x:c r="E55" s="109" t="str">
-        <x:v>Level and increasing annuities, immunisation and duration concepts</x:v>
+        <x:v>Long and short-term finance, share issues, debt, leasing and working capital</x:v>
       </x:c>
       <x:c r="F55" s="109" t="str">
-        <x:v>Revisit annuities and duration from memory, then target the weakest sub-area.</x:v>
+        <x:v>Revisit raising finance from memory, then target the weakest sub-area.</x:v>
       </x:c>
       <x:c r="G55" s="109" t="str">
         <x:v>Redo open errors first, then complete another timed mixed set without relying on notes.</x:v>
@@ -4313,7 +4313,7 @@
         <x:v>Repeat the applied task from a blank file or extend it with an independent check or sensitivity.</x:v>
       </x:c>
       <x:c r="I55" s="109" t="n">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="J55" s="109"/>
       <x:c r="K55" s="109"/>
@@ -4329,22 +4329,22 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="D56" s="109" t="str">
-        <x:v>Single-life models</x:v>
+        <x:v>Accounts foundations</x:v>
       </x:c>
       <x:c r="E56" s="109" t="str">
-        <x:v>Survival probabilities, life tables, assurance and annuity values</x:v>
+        <x:v>Statement of profit or loss, financial position and cash flows</x:v>
       </x:c>
       <x:c r="F56" s="109" t="str">
-        <x:v>Convert symbols to a timeline and annotate the contingent payment condition.</x:v>
+        <x:v>Reconstruct the three statements from a blank template.</x:v>
       </x:c>
       <x:c r="G56" s="109" t="str">
-        <x:v>Practise life-contingency questions and rewrite any weak setup.</x:v>
+        <x:v>Complete an accounts-building question and reconcile every total.</x:v>
       </x:c>
       <x:c r="H56" s="109" t="str">
-        <x:v>Calculate life annuity values from a supplied table.</x:v>
+        <x:v>Create an accounts template with balance checks.</x:v>
       </x:c>
       <x:c r="I56" s="109" t="n">
-        <x:v>20</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="J56" s="109"/>
       <x:c r="K56" s="109"/>
@@ -4360,19 +4360,19 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D57" s="109" t="str">
-        <x:v>Multiple lives and decrements</x:v>
+        <x:v>Accounts construction and groups</x:v>
       </x:c>
       <x:c r="E57" s="109" t="str">
-        <x:v>Joint-life, last-survivor, multiple-decrement and select models</x:v>
+        <x:v>Adjustments, group accounts, insurance and bank accounts</x:v>
       </x:c>
       <x:c r="F57" s="109" t="str">
-        <x:v>Write a decision tree for the status and payment trigger.</x:v>
+        <x:v>Write an adjustment checklist before starting any construction question.</x:v>
       </x:c>
       <x:c r="G57" s="109" t="str">
-        <x:v>Attempt a longer multi-part question and audit the notation.</x:v>
+        <x:v>Attempt a longer multi-part construction question.</x:v>
       </x:c>
       <x:c r="H57" s="109" t="str">
-        <x:v>Model decrement probabilities and test that probabilities reconcile.</x:v>
+        <x:v>Use a spreadsheet to separate adjustments from final statements.</x:v>
       </x:c>
       <x:c r="I57" s="109" t="n">
         <x:v>20</x:v>
@@ -4391,19 +4391,19 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D58" s="109" t="str">
-        <x:v>Pricing and reserving</x:v>
+        <x:v>Interpreting accounts</x:v>
       </x:c>
       <x:c r="E58" s="109" t="str">
-        <x:v>Net premiums, gross premiums, prospective and retrospective reserves</x:v>
+        <x:v>Ratios, trends, limitations and investor analysis</x:v>
       </x:c>
       <x:c r="F58" s="109" t="str">
-        <x:v>For each formula, state what is being valued, at what time and on what basis.</x:v>
+        <x:v>Use a claim-evidence-conclusion structure for every interpretation paragraph.</x:v>
       </x:c>
       <x:c r="G58" s="109" t="str">
-        <x:v>Complete premium and reserve questions to a strict time budget.</x:v>
+        <x:v>Complete a ratio question, then improve the quality of the narrative answer.</x:v>
       </x:c>
       <x:c r="H58" s="109" t="str">
-        <x:v>Build a reserve roll-forward and investigate each movement.</x:v>
+        <x:v>Calculate and graph a ratio trend from a small data table.</x:v>
       </x:c>
       <x:c r="I58" s="109" t="n">
         <x:v>9</x:v>
@@ -4422,13 +4422,13 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D59" s="109" t="str">
-        <x:v>Pricing and reserving</x:v>
+        <x:v>Interpreting accounts</x:v>
       </x:c>
       <x:c r="E59" s="109" t="str">
-        <x:v>Net premiums, gross premiums, prospective and retrospective reserves</x:v>
+        <x:v>Ratios, trends, limitations and investor analysis</x:v>
       </x:c>
       <x:c r="F59" s="109" t="str">
-        <x:v>Revisit pricing and reserving from memory, then target the weakest sub-area.</x:v>
+        <x:v>Revisit interpreting accounts from memory, then target the weakest sub-area.</x:v>
       </x:c>
       <x:c r="G59" s="109" t="str">
         <x:v>Redo open errors first, then complete another timed mixed set without relying on notes.</x:v>
@@ -4453,22 +4453,22 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="D60" s="109" t="str">
-        <x:v>Integrated exam practice</x:v>
+        <x:v>Capital structure and growth</x:v>
       </x:c>
       <x:c r="E60" s="109" t="str">
-        <x:v>Mixed CM1 applications, answer structure and weak-area repair</x:v>
+        <x:v>Derivatives, restructuring, WACC, dividend policy and acquisition</x:v>
       </x:c>
       <x:c r="F60" s="109" t="str">
-        <x:v>Choose three recurring error themes and revisit them before comfortable topics.</x:v>
+        <x:v>Create a decision tree for financing and restructuring recommendations.</x:v>
       </x:c>
       <x:c r="G60" s="109" t="str">
-        <x:v>Complete a substantial timed Paper A-style set and self-mark your method.</x:v>
+        <x:v>Complete applied finance questions including a WACC calculation.</x:v>
       </x:c>
       <x:c r="H60" s="109" t="str">
-        <x:v>Complete a timed Excel challenge and check formulas independently.</x:v>
+        <x:v>Build a WACC sensitivity table.</x:v>
       </x:c>
       <x:c r="I60" s="109" t="n">
-        <x:v>25</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="J60" s="109"/>
       <x:c r="K60" s="109"/>
@@ -4484,22 +4484,22 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="D61" s="109" t="str">
-        <x:v>Mock and consolidation</x:v>
+        <x:v>Project appraisal and mock</x:v>
       </x:c>
       <x:c r="E61" s="109" t="str">
-        <x:v>Whole syllabus, timed practice and final weak-area repair</x:v>
+        <x:v>NPV, IRR, risk, capital projects and whole-syllabus consolidation</x:v>
       </x:c>
       <x:c r="F61" s="109" t="str">
-        <x:v>Create a final formula and notation sheet from memory, then correct it.</x:v>
+        <x:v>Prepare an investment-appraisal checklist and a final error list.</x:v>
       </x:c>
       <x:c r="G61" s="109" t="str">
-        <x:v>Sit a full mock or equivalent timed set, then separate marking from error correction.</x:v>
+        <x:v>Complete a timed mock or equivalent mixed set, then redraft weak written answers.</x:v>
       </x:c>
       <x:c r="H61" s="109" t="str">
-        <x:v>Rebuild the weakest modelling task from a blank workbook.</x:v>
+        <x:v>Build an NPV model and test a key sensitivity.</x:v>
       </x:c>
       <x:c r="I61" s="109" t="n">
-        <x:v>30</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="J61" s="109"/>
       <x:c r="K61" s="109"/>
@@ -4515,22 +4515,22 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="D62" s="109" t="str">
-        <x:v>Theory of interest rates</x:v>
+        <x:v>Governance and objectives</x:v>
       </x:c>
       <x:c r="E62" s="109" t="str">
-        <x:v>Rate conversions, discount functions, force of interest and term structures</x:v>
+        <x:v>Corporate governance, ethics, stakeholders and shareholder wealth</x:v>
       </x:c>
       <x:c r="F62" s="109" t="str">
-        <x:v>Build a one-page rate-conversion sheet and derive each relationship once.</x:v>
+        <x:v>Create a stakeholder-conflict grid and a governance answer plan.</x:v>
       </x:c>
       <x:c r="G62" s="109" t="str">
-        <x:v>Complete short calculations and mark units and timing explicitly.</x:v>
+        <x:v>Write short applied explanations and self-check for a direct conclusion.</x:v>
       </x:c>
       <x:c r="H62" s="109" t="str">
-        <x:v>Create a simple cashflow-discounting model in Excel.</x:v>
+        <x:v>Build a one-page summary of key distinctions and common command words.</x:v>
       </x:c>
       <x:c r="I62" s="109" t="n">
-        <x:v>10</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="J62" s="109"/>
       <x:c r="K62" s="109"/>
@@ -4546,13 +4546,13 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="D63" s="109" t="str">
-        <x:v>Theory of interest rates</x:v>
+        <x:v>Governance and objectives</x:v>
       </x:c>
       <x:c r="E63" s="109" t="str">
-        <x:v>Rate conversions, discount functions, force of interest and term structures</x:v>
+        <x:v>Corporate governance, ethics, stakeholders and shareholder wealth</x:v>
       </x:c>
       <x:c r="F63" s="109" t="str">
-        <x:v>Revisit theory of interest rates from memory, then target the weakest sub-area.</x:v>
+        <x:v>Revisit governance and objectives from memory, then target the weakest sub-area.</x:v>
       </x:c>
       <x:c r="G63" s="109" t="str">
         <x:v>Redo open errors first, then complete another timed mixed set without relying on notes.</x:v>
@@ -4561,7 +4561,7 @@
         <x:v>Repeat the applied task from a blank file or extend it with an independent check or sensitivity.</x:v>
       </x:c>
       <x:c r="I63" s="109" t="n">
-        <x:v>10</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="J63" s="109"/>
       <x:c r="K63" s="109"/>
@@ -4577,19 +4577,19 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="D64" s="109" t="str">
-        <x:v>Equation of value and loans</x:v>
+        <x:v>Business ownership and taxation</x:v>
       </x:c>
       <x:c r="E64" s="109" t="str">
-        <x:v>Cashflow valuation, loans, outstanding balances, bonds and yield</x:v>
+        <x:v>Business forms, ownership, tax and corporate structure</x:v>
       </x:c>
       <x:c r="F64" s="109" t="str">
-        <x:v>Draw every cashflow timeline before calculating and practise two methods for loan questions.</x:v>
+        <x:v>Compare each legal form by ownership, risk, capital and control.</x:v>
       </x:c>
       <x:c r="G64" s="109" t="str">
-        <x:v>Complete mixed loan and bond questions under time pressure.</x:v>
+        <x:v>Complete scenario questions requiring a justified recommendation.</x:v>
       </x:c>
       <x:c r="H64" s="109" t="str">
-        <x:v>Build a loan schedule with a rate input and balance check.</x:v>
+        <x:v>Use a simple table to compare tax or cashflow implications.</x:v>
       </x:c>
       <x:c r="I64" s="109" t="n">
         <x:v>18</x:v>
@@ -4608,22 +4608,22 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="D65" s="109" t="str">
-        <x:v>Annuities and duration</x:v>
+        <x:v>Raising finance</x:v>
       </x:c>
       <x:c r="E65" s="109" t="str">
-        <x:v>Level and increasing annuities, immunisation and duration concepts</x:v>
+        <x:v>Long and short-term finance, share issues, debt, leasing and working capital</x:v>
       </x:c>
       <x:c r="F65" s="109" t="str">
-        <x:v>Create a formula map and a list of common timing traps.</x:v>
+        <x:v>Create a finance-source comparison: cost, risk, control, flexibility and timing.</x:v>
       </x:c>
       <x:c r="G65" s="109" t="str">
-        <x:v>Attempt a timed mixed interest-rate set.</x:v>
+        <x:v>Complete finance-choice questions with a stated recommendation.</x:v>
       </x:c>
       <x:c r="H65" s="109" t="str">
-        <x:v>Use Excel to compare present values under alternative interest-rate scenarios.</x:v>
+        <x:v>Calculate a lease or short-term financing comparison.</x:v>
       </x:c>
       <x:c r="I65" s="109" t="n">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="J65" s="109"/>
       <x:c r="K65" s="109"/>
@@ -4639,13 +4639,13 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="D66" s="109" t="str">
-        <x:v>Annuities and duration</x:v>
+        <x:v>Raising finance</x:v>
       </x:c>
       <x:c r="E66" s="109" t="str">
-        <x:v>Level and increasing annuities, immunisation and duration concepts</x:v>
+        <x:v>Long and short-term finance, share issues, debt, leasing and working capital</x:v>
       </x:c>
       <x:c r="F66" s="109" t="str">
-        <x:v>Revisit annuities and duration from memory, then target the weakest sub-area.</x:v>
+        <x:v>Revisit raising finance from memory, then target the weakest sub-area.</x:v>
       </x:c>
       <x:c r="G66" s="109" t="str">
         <x:v>Redo open errors first, then complete another timed mixed set without relying on notes.</x:v>
@@ -4654,7 +4654,7 @@
         <x:v>Repeat the applied task from a blank file or extend it with an independent check or sensitivity.</x:v>
       </x:c>
       <x:c r="I66" s="109" t="n">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="J66" s="109"/>
       <x:c r="K66" s="109"/>
@@ -4670,22 +4670,22 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="D67" s="109" t="str">
-        <x:v>Single-life models</x:v>
+        <x:v>Accounts foundations</x:v>
       </x:c>
       <x:c r="E67" s="109" t="str">
-        <x:v>Survival probabilities, life tables, assurance and annuity values</x:v>
+        <x:v>Statement of profit or loss, financial position and cash flows</x:v>
       </x:c>
       <x:c r="F67" s="109" t="str">
-        <x:v>Convert symbols to a timeline and annotate the contingent payment condition.</x:v>
+        <x:v>Reconstruct the three statements from a blank template.</x:v>
       </x:c>
       <x:c r="G67" s="109" t="str">
-        <x:v>Practise life-contingency questions and rewrite any weak setup.</x:v>
+        <x:v>Complete an accounts-building question and reconcile every total.</x:v>
       </x:c>
       <x:c r="H67" s="109" t="str">
-        <x:v>Calculate life annuity values from a supplied table.</x:v>
+        <x:v>Create an accounts template with balance checks.</x:v>
       </x:c>
       <x:c r="I67" s="109" t="n">
-        <x:v>20</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="J67" s="109"/>
       <x:c r="K67" s="109"/>
@@ -4701,19 +4701,19 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D68" s="109" t="str">
-        <x:v>Multiple lives and decrements</x:v>
+        <x:v>Accounts construction and groups</x:v>
       </x:c>
       <x:c r="E68" s="109" t="str">
-        <x:v>Joint-life, last-survivor, multiple-decrement and select models</x:v>
+        <x:v>Adjustments, group accounts, insurance and bank accounts</x:v>
       </x:c>
       <x:c r="F68" s="109" t="str">
-        <x:v>Write a decision tree for the status and payment trigger.</x:v>
+        <x:v>Write an adjustment checklist before starting any construction question.</x:v>
       </x:c>
       <x:c r="G68" s="109" t="str">
-        <x:v>Attempt a longer multi-part question and audit the notation.</x:v>
+        <x:v>Attempt a longer multi-part construction question.</x:v>
       </x:c>
       <x:c r="H68" s="109" t="str">
-        <x:v>Model decrement probabilities and test that probabilities reconcile.</x:v>
+        <x:v>Use a spreadsheet to separate adjustments from final statements.</x:v>
       </x:c>
       <x:c r="I68" s="109" t="n">
         <x:v>10</x:v>
@@ -4732,13 +4732,13 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D69" s="109" t="str">
-        <x:v>Multiple lives and decrements</x:v>
+        <x:v>Accounts construction and groups</x:v>
       </x:c>
       <x:c r="E69" s="109" t="str">
-        <x:v>Joint-life, last-survivor, multiple-decrement and select models</x:v>
+        <x:v>Adjustments, group accounts, insurance and bank accounts</x:v>
       </x:c>
       <x:c r="F69" s="109" t="str">
-        <x:v>Revisit multiple lives and decrements from memory, then target the weakest sub-area.</x:v>
+        <x:v>Revisit accounts construction and groups from memory, then target the weakest sub-area.</x:v>
       </x:c>
       <x:c r="G69" s="109" t="str">
         <x:v>Redo open errors first, then complete another timed mixed set without relying on notes.</x:v>
@@ -4763,19 +4763,19 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D70" s="109" t="str">
-        <x:v>Pricing and reserving</x:v>
+        <x:v>Interpreting accounts</x:v>
       </x:c>
       <x:c r="E70" s="109" t="str">
-        <x:v>Net premiums, gross premiums, prospective and retrospective reserves</x:v>
+        <x:v>Ratios, trends, limitations and investor analysis</x:v>
       </x:c>
       <x:c r="F70" s="109" t="str">
-        <x:v>For each formula, state what is being valued, at what time and on what basis.</x:v>
+        <x:v>Use a claim-evidence-conclusion structure for every interpretation paragraph.</x:v>
       </x:c>
       <x:c r="G70" s="109" t="str">
-        <x:v>Complete premium and reserve questions to a strict time budget.</x:v>
+        <x:v>Complete a ratio question, then improve the quality of the narrative answer.</x:v>
       </x:c>
       <x:c r="H70" s="109" t="str">
-        <x:v>Build a reserve roll-forward and investigate each movement.</x:v>
+        <x:v>Calculate and graph a ratio trend from a small data table.</x:v>
       </x:c>
       <x:c r="I70" s="109" t="n">
         <x:v>18</x:v>
@@ -4794,22 +4794,22 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="D71" s="109" t="str">
-        <x:v>Integrated exam practice</x:v>
+        <x:v>Capital structure and growth</x:v>
       </x:c>
       <x:c r="E71" s="109" t="str">
-        <x:v>Mixed CM1 applications, answer structure and weak-area repair</x:v>
+        <x:v>Derivatives, restructuring, WACC, dividend policy and acquisition</x:v>
       </x:c>
       <x:c r="F71" s="109" t="str">
-        <x:v>Choose three recurring error themes and revisit them before comfortable topics.</x:v>
+        <x:v>Create a decision tree for financing and restructuring recommendations.</x:v>
       </x:c>
       <x:c r="G71" s="109" t="str">
-        <x:v>Complete a substantial timed Paper A-style set and self-mark your method.</x:v>
+        <x:v>Complete applied finance questions including a WACC calculation.</x:v>
       </x:c>
       <x:c r="H71" s="109" t="str">
-        <x:v>Complete a timed Excel challenge and check formulas independently.</x:v>
+        <x:v>Build a WACC sensitivity table.</x:v>
       </x:c>
       <x:c r="I71" s="109" t="n">
-        <x:v>13</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="J71" s="109"/>
       <x:c r="K71" s="109"/>
@@ -4825,13 +4825,13 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="D72" s="109" t="str">
-        <x:v>Integrated exam practice</x:v>
+        <x:v>Capital structure and growth</x:v>
       </x:c>
       <x:c r="E72" s="109" t="str">
-        <x:v>Mixed CM1 applications, answer structure and weak-area repair</x:v>
+        <x:v>Derivatives, restructuring, WACC, dividend policy and acquisition</x:v>
       </x:c>
       <x:c r="F72" s="109" t="str">
-        <x:v>Revisit integrated exam practice from memory, then target the weakest sub-area.</x:v>
+        <x:v>Revisit capital structure and growth from memory, then target the weakest sub-area.</x:v>
       </x:c>
       <x:c r="G72" s="109" t="str">
         <x:v>Redo open errors first, then complete another timed mixed set without relying on notes.</x:v>
@@ -4840,7 +4840,7 @@
         <x:v>Repeat the applied task from a blank file or extend it with an independent check or sensitivity.</x:v>
       </x:c>
       <x:c r="I72" s="109" t="n">
-        <x:v>12</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="J72" s="109"/>
       <x:c r="K72" s="109"/>
@@ -4856,22 +4856,22 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="D73" s="109" t="str">
-        <x:v>Mock and consolidation</x:v>
+        <x:v>Project appraisal and mock</x:v>
       </x:c>
       <x:c r="E73" s="109" t="str">
-        <x:v>Whole syllabus, timed practice and final weak-area repair</x:v>
+        <x:v>NPV, IRR, risk, capital projects and whole-syllabus consolidation</x:v>
       </x:c>
       <x:c r="F73" s="109" t="str">
-        <x:v>Create a final formula and notation sheet from memory, then correct it.</x:v>
+        <x:v>Prepare an investment-appraisal checklist and a final error list.</x:v>
       </x:c>
       <x:c r="G73" s="109" t="str">
-        <x:v>Sit a full mock or equivalent timed set, then separate marking from error correction.</x:v>
+        <x:v>Complete a timed mock or equivalent mixed set, then redraft weak written answers.</x:v>
       </x:c>
       <x:c r="H73" s="109" t="str">
-        <x:v>Rebuild the weakest modelling task from a blank workbook.</x:v>
+        <x:v>Build an NPV model and test a key sensitivity.</x:v>
       </x:c>
       <x:c r="I73" s="109" t="n">
-        <x:v>30</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="J73" s="109"/>
       <x:c r="K73" s="109"/>
@@ -4887,22 +4887,22 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="D74" s="109" t="str">
-        <x:v>Theory of interest rates</x:v>
+        <x:v>Governance and objectives</x:v>
       </x:c>
       <x:c r="E74" s="109" t="str">
-        <x:v>Rate conversions, discount functions, force of interest and term structures</x:v>
+        <x:v>Corporate governance, ethics, stakeholders and shareholder wealth</x:v>
       </x:c>
       <x:c r="F74" s="109" t="str">
-        <x:v>Build a one-page rate-conversion sheet and derive each relationship once.</x:v>
+        <x:v>Create a stakeholder-conflict grid and a governance answer plan.</x:v>
       </x:c>
       <x:c r="G74" s="109" t="str">
-        <x:v>Complete short calculations and mark units and timing explicitly.</x:v>
+        <x:v>Write short applied explanations and self-check for a direct conclusion.</x:v>
       </x:c>
       <x:c r="H74" s="109" t="str">
-        <x:v>Create a simple cashflow-discounting model in Excel.</x:v>
+        <x:v>Build a one-page summary of key distinctions and common command words.</x:v>
       </x:c>
       <x:c r="I74" s="109" t="n">
-        <x:v>10</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="J74" s="109"/>
       <x:c r="K74" s="109"/>
@@ -4918,13 +4918,13 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="D75" s="109" t="str">
-        <x:v>Theory of interest rates</x:v>
+        <x:v>Governance and objectives</x:v>
       </x:c>
       <x:c r="E75" s="109" t="str">
-        <x:v>Rate conversions, discount functions, force of interest and term structures</x:v>
+        <x:v>Corporate governance, ethics, stakeholders and shareholder wealth</x:v>
       </x:c>
       <x:c r="F75" s="109" t="str">
-        <x:v>Revisit theory of interest rates from memory, then target the weakest sub-area.</x:v>
+        <x:v>Revisit governance and objectives from memory, then target the weakest sub-area.</x:v>
       </x:c>
       <x:c r="G75" s="109" t="str">
         <x:v>Redo open errors first, then complete another timed mixed set without relying on notes.</x:v>
@@ -4933,7 +4933,7 @@
         <x:v>Repeat the applied task from a blank file or extend it with an independent check or sensitivity.</x:v>
       </x:c>
       <x:c r="I75" s="109" t="n">
-        <x:v>10</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="J75" s="109"/>
       <x:c r="K75" s="109"/>
@@ -4949,19 +4949,19 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="D76" s="109" t="str">
-        <x:v>Equation of value and loans</x:v>
+        <x:v>Business ownership and taxation</x:v>
       </x:c>
       <x:c r="E76" s="109" t="str">
-        <x:v>Cashflow valuation, loans, outstanding balances, bonds and yield</x:v>
+        <x:v>Business forms, ownership, tax and corporate structure</x:v>
       </x:c>
       <x:c r="F76" s="109" t="str">
-        <x:v>Draw every cashflow timeline before calculating and practise two methods for loan questions.</x:v>
+        <x:v>Compare each legal form by ownership, risk, capital and control.</x:v>
       </x:c>
       <x:c r="G76" s="109" t="str">
-        <x:v>Complete mixed loan and bond questions under time pressure.</x:v>
+        <x:v>Complete scenario questions requiring a justified recommendation.</x:v>
       </x:c>
       <x:c r="H76" s="109" t="str">
-        <x:v>Build a loan schedule with a rate input and balance check.</x:v>
+        <x:v>Use a simple table to compare tax or cashflow implications.</x:v>
       </x:c>
       <x:c r="I76" s="109" t="n">
         <x:v>9</x:v>
@@ -4980,13 +4980,13 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="D77" s="109" t="str">
-        <x:v>Equation of value and loans</x:v>
+        <x:v>Business ownership and taxation</x:v>
       </x:c>
       <x:c r="E77" s="109" t="str">
-        <x:v>Cashflow valuation, loans, outstanding balances, bonds and yield</x:v>
+        <x:v>Business forms, ownership, tax and corporate structure</x:v>
       </x:c>
       <x:c r="F77" s="109" t="str">
-        <x:v>Revisit equation of value and loans from memory, then target the weakest sub-area.</x:v>
+        <x:v>Revisit business ownership and taxation from memory, then target the weakest sub-area.</x:v>
       </x:c>
       <x:c r="G77" s="109" t="str">
         <x:v>Redo open errors first, then complete another timed mixed set without relying on notes.</x:v>
@@ -5011,22 +5011,22 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="D78" s="109" t="str">
-        <x:v>Annuities and duration</x:v>
+        <x:v>Raising finance</x:v>
       </x:c>
       <x:c r="E78" s="109" t="str">
-        <x:v>Level and increasing annuities, immunisation and duration concepts</x:v>
+        <x:v>Long and short-term finance, share issues, debt, leasing and working capital</x:v>
       </x:c>
       <x:c r="F78" s="109" t="str">
-        <x:v>Create a formula map and a list of common timing traps.</x:v>
+        <x:v>Create a finance-source comparison: cost, risk, control, flexibility and timing.</x:v>
       </x:c>
       <x:c r="G78" s="109" t="str">
-        <x:v>Attempt a timed mixed interest-rate set.</x:v>
+        <x:v>Complete finance-choice questions with a stated recommendation.</x:v>
       </x:c>
       <x:c r="H78" s="109" t="str">
-        <x:v>Use Excel to compare present values under alternative interest-rate scenarios.</x:v>
+        <x:v>Calculate a lease or short-term financing comparison.</x:v>
       </x:c>
       <x:c r="I78" s="109" t="n">
-        <x:v>18</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="J78" s="109"/>
       <x:c r="K78" s="109"/>
@@ -5042,22 +5042,22 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="D79" s="109" t="str">
-        <x:v>Single-life models</x:v>
+        <x:v>Accounts foundations</x:v>
       </x:c>
       <x:c r="E79" s="109" t="str">
-        <x:v>Survival probabilities, life tables, assurance and annuity values</x:v>
+        <x:v>Statement of profit or loss, financial position and cash flows</x:v>
       </x:c>
       <x:c r="F79" s="109" t="str">
-        <x:v>Convert symbols to a timeline and annotate the contingent payment condition.</x:v>
+        <x:v>Reconstruct the three statements from a blank template.</x:v>
       </x:c>
       <x:c r="G79" s="109" t="str">
-        <x:v>Practise life-contingency questions and rewrite any weak setup.</x:v>
+        <x:v>Complete an accounts-building question and reconcile every total.</x:v>
       </x:c>
       <x:c r="H79" s="109" t="str">
-        <x:v>Calculate life annuity values from a supplied table.</x:v>
+        <x:v>Create an accounts template with balance checks.</x:v>
       </x:c>
       <x:c r="I79" s="109" t="n">
-        <x:v>10</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="J79" s="109"/>
       <x:c r="K79" s="109"/>
@@ -5073,13 +5073,13 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D80" s="109" t="str">
-        <x:v>Single-life models</x:v>
+        <x:v>Accounts foundations</x:v>
       </x:c>
       <x:c r="E80" s="109" t="str">
-        <x:v>Survival probabilities, life tables, assurance and annuity values</x:v>
+        <x:v>Statement of profit or loss, financial position and cash flows</x:v>
       </x:c>
       <x:c r="F80" s="109" t="str">
-        <x:v>Revisit single-life models from memory, then target the weakest sub-area.</x:v>
+        <x:v>Revisit accounts foundations from memory, then target the weakest sub-area.</x:v>
       </x:c>
       <x:c r="G80" s="109" t="str">
         <x:v>Redo open errors first, then complete another timed mixed set without relying on notes.</x:v>
@@ -5088,7 +5088,7 @@
         <x:v>Repeat the applied task from a blank file or extend it with an independent check or sensitivity.</x:v>
       </x:c>
       <x:c r="I80" s="109" t="n">
-        <x:v>10</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="J80" s="109"/>
       <x:c r="K80" s="109"/>
@@ -5104,19 +5104,19 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D81" s="109" t="str">
-        <x:v>Multiple lives and decrements</x:v>
+        <x:v>Accounts construction and groups</x:v>
       </x:c>
       <x:c r="E81" s="109" t="str">
-        <x:v>Joint-life, last-survivor, multiple-decrement and select models</x:v>
+        <x:v>Adjustments, group accounts, insurance and bank accounts</x:v>
       </x:c>
       <x:c r="F81" s="109" t="str">
-        <x:v>Write a decision tree for the status and payment trigger.</x:v>
+        <x:v>Write an adjustment checklist before starting any construction question.</x:v>
       </x:c>
       <x:c r="G81" s="109" t="str">
-        <x:v>Attempt a longer multi-part question and audit the notation.</x:v>
+        <x:v>Attempt a longer multi-part construction question.</x:v>
       </x:c>
       <x:c r="H81" s="109" t="str">
-        <x:v>Model decrement probabilities and test that probabilities reconcile.</x:v>
+        <x:v>Use a spreadsheet to separate adjustments from final statements.</x:v>
       </x:c>
       <x:c r="I81" s="109" t="n">
         <x:v>10</x:v>
@@ -5135,13 +5135,13 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D82" s="109" t="str">
-        <x:v>Multiple lives and decrements</x:v>
+        <x:v>Accounts construction and groups</x:v>
       </x:c>
       <x:c r="E82" s="109" t="str">
-        <x:v>Joint-life, last-survivor, multiple-decrement and select models</x:v>
+        <x:v>Adjustments, group accounts, insurance and bank accounts</x:v>
       </x:c>
       <x:c r="F82" s="109" t="str">
-        <x:v>Revisit multiple lives and decrements from memory, then target the weakest sub-area.</x:v>
+        <x:v>Revisit accounts construction and groups from memory, then target the weakest sub-area.</x:v>
       </x:c>
       <x:c r="G82" s="109" t="str">
         <x:v>Redo open errors first, then complete another timed mixed set without relying on notes.</x:v>
@@ -5166,19 +5166,19 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="D83" s="109" t="str">
-        <x:v>Pricing and reserving</x:v>
+        <x:v>Interpreting accounts</x:v>
       </x:c>
       <x:c r="E83" s="109" t="str">
-        <x:v>Net premiums, gross premiums, prospective and retrospective reserves</x:v>
+        <x:v>Ratios, trends, limitations and investor analysis</x:v>
       </x:c>
       <x:c r="F83" s="109" t="str">
-        <x:v>For each formula, state what is being valued, at what time and on what basis.</x:v>
+        <x:v>Use a claim-evidence-conclusion structure for every interpretation paragraph.</x:v>
       </x:c>
       <x:c r="G83" s="109" t="str">
-        <x:v>Complete premium and reserve questions to a strict time budget.</x:v>
+        <x:v>Complete a ratio question, then improve the quality of the narrative answer.</x:v>
       </x:c>
       <x:c r="H83" s="109" t="str">
-        <x:v>Build a reserve roll-forward and investigate each movement.</x:v>
+        <x:v>Calculate and graph a ratio trend from a small data table.</x:v>
       </x:c>
       <x:c r="I83" s="109" t="n">
         <x:v>18</x:v>
@@ -5197,22 +5197,22 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="D84" s="109" t="str">
-        <x:v>Integrated exam practice</x:v>
+        <x:v>Capital structure and growth</x:v>
       </x:c>
       <x:c r="E84" s="109" t="str">
-        <x:v>Mixed CM1 applications, answer structure and weak-area repair</x:v>
+        <x:v>Derivatives, restructuring, WACC, dividend policy and acquisition</x:v>
       </x:c>
       <x:c r="F84" s="109" t="str">
-        <x:v>Choose three recurring error themes and revisit them before comfortable topics.</x:v>
+        <x:v>Create a decision tree for financing and restructuring recommendations.</x:v>
       </x:c>
       <x:c r="G84" s="109" t="str">
-        <x:v>Complete a substantial timed Paper A-style set and self-mark your method.</x:v>
+        <x:v>Complete applied finance questions including a WACC calculation.</x:v>
       </x:c>
       <x:c r="H84" s="109" t="str">
-        <x:v>Complete a timed Excel challenge and check formulas independently.</x:v>
+        <x:v>Build a WACC sensitivity table.</x:v>
       </x:c>
       <x:c r="I84" s="109" t="n">
-        <x:v>13</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="J84" s="109"/>
       <x:c r="K84" s="109"/>
@@ -5228,13 +5228,13 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="D85" s="109" t="str">
-        <x:v>Integrated exam practice</x:v>
+        <x:v>Capital structure and growth</x:v>
       </x:c>
       <x:c r="E85" s="109" t="str">
-        <x:v>Mixed CM1 applications, answer structure and weak-area repair</x:v>
+        <x:v>Derivatives, restructuring, WACC, dividend policy and acquisition</x:v>
       </x:c>
       <x:c r="F85" s="109" t="str">
-        <x:v>Revisit integrated exam practice from memory, then target the weakest sub-area.</x:v>
+        <x:v>Revisit capital structure and growth from memory, then target the weakest sub-area.</x:v>
       </x:c>
       <x:c r="G85" s="109" t="str">
         <x:v>Redo open errors first, then complete another timed mixed set without relying on notes.</x:v>
@@ -5243,7 +5243,7 @@
         <x:v>Repeat the applied task from a blank file or extend it with an independent check or sensitivity.</x:v>
       </x:c>
       <x:c r="I85" s="109" t="n">
-        <x:v>12</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="J85" s="109"/>
       <x:c r="K85" s="109"/>
@@ -5259,22 +5259,22 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="D86" s="109" t="str">
-        <x:v>Mock and consolidation</x:v>
+        <x:v>Project appraisal and mock</x:v>
       </x:c>
       <x:c r="E86" s="109" t="str">
-        <x:v>Whole syllabus, timed practice and final weak-area repair</x:v>
+        <x:v>NPV, IRR, risk, capital projects and whole-syllabus consolidation</x:v>
       </x:c>
       <x:c r="F86" s="109" t="str">
-        <x:v>Create a final formula and notation sheet from memory, then correct it.</x:v>
+        <x:v>Prepare an investment-appraisal checklist and a final error list.</x:v>
       </x:c>
       <x:c r="G86" s="109" t="str">
-        <x:v>Sit a full mock or equivalent timed set, then separate marking from error correction.</x:v>
+        <x:v>Complete a timed mock or equivalent mixed set, then redraft weak written answers.</x:v>
       </x:c>
       <x:c r="H86" s="109" t="str">
-        <x:v>Rebuild the weakest modelling task from a blank workbook.</x:v>
+        <x:v>Build an NPV model and test a key sensitivity.</x:v>
       </x:c>
       <x:c r="I86" s="109" t="n">
-        <x:v>30</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="J86" s="109"/>
       <x:c r="K86" s="109"/>
@@ -5290,22 +5290,22 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="D87" s="109" t="str">
-        <x:v>Theory of interest rates</x:v>
+        <x:v>Governance and objectives</x:v>
       </x:c>
       <x:c r="E87" s="109" t="str">
-        <x:v>Rate conversions, discount functions, force of interest and term structures</x:v>
+        <x:v>Corporate governance, ethics, stakeholders and shareholder wealth</x:v>
       </x:c>
       <x:c r="F87" s="109" t="str">
-        <x:v>Build a one-page rate-conversion sheet and derive each relationship once.</x:v>
+        <x:v>Create a stakeholder-conflict grid and a governance answer plan.</x:v>
       </x:c>
       <x:c r="G87" s="109" t="str">
-        <x:v>Complete short calculations and mark units and timing explicitly.</x:v>
+        <x:v>Write short applied explanations and self-check for a direct conclusion.</x:v>
       </x:c>
       <x:c r="H87" s="109" t="str">
-        <x:v>Create a simple cashflow-discounting model in Excel.</x:v>
+        <x:v>Build a one-page summary of key distinctions and common command words.</x:v>
       </x:c>
       <x:c r="I87" s="109" t="n">
-        <x:v>10</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="J87" s="109"/>
       <x:c r="K87" s="109"/>
@@ -5321,13 +5321,13 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="D88" s="109" t="str">
-        <x:v>Theory of interest rates</x:v>
+        <x:v>Governance and objectives</x:v>
       </x:c>
       <x:c r="E88" s="109" t="str">
-        <x:v>Rate conversions, discount functions, force of interest and term structures</x:v>
+        <x:v>Corporate governance, ethics, stakeholders and shareholder wealth</x:v>
       </x:c>
       <x:c r="F88" s="109" t="str">
-        <x:v>Revisit theory of interest rates from memory, then target the weakest sub-area.</x:v>
+        <x:v>Revisit governance and objectives from memory, then target the weakest sub-area.</x:v>
       </x:c>
       <x:c r="G88" s="109" t="str">
         <x:v>Redo open errors first, then complete another timed mixed set without relying on notes.</x:v>
@@ -5336,7 +5336,7 @@
         <x:v>Repeat the applied task from a blank file or extend it with an independent check or sensitivity.</x:v>
       </x:c>
       <x:c r="I88" s="109" t="n">
-        <x:v>10</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="J88" s="109"/>
       <x:c r="K88" s="109"/>
@@ -5352,19 +5352,19 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="D89" s="109" t="str">
-        <x:v>Equation of value and loans</x:v>
+        <x:v>Business ownership and taxation</x:v>
       </x:c>
       <x:c r="E89" s="109" t="str">
-        <x:v>Cashflow valuation, loans, outstanding balances, bonds and yield</x:v>
+        <x:v>Business forms, ownership, tax and corporate structure</x:v>
       </x:c>
       <x:c r="F89" s="109" t="str">
-        <x:v>Draw every cashflow timeline before calculating and practise two methods for loan questions.</x:v>
+        <x:v>Compare each legal form by ownership, risk, capital and control.</x:v>
       </x:c>
       <x:c r="G89" s="109" t="str">
-        <x:v>Complete mixed loan and bond questions under time pressure.</x:v>
+        <x:v>Complete scenario questions requiring a justified recommendation.</x:v>
       </x:c>
       <x:c r="H89" s="109" t="str">
-        <x:v>Build a loan schedule with a rate input and balance check.</x:v>
+        <x:v>Use a simple table to compare tax or cashflow implications.</x:v>
       </x:c>
       <x:c r="I89" s="109" t="n">
         <x:v>9</x:v>
@@ -5383,13 +5383,13 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="D90" s="109" t="str">
-        <x:v>Equation of value and loans</x:v>
+        <x:v>Business ownership and taxation</x:v>
       </x:c>
       <x:c r="E90" s="109" t="str">
-        <x:v>Cashflow valuation, loans, outstanding balances, bonds and yield</x:v>
+        <x:v>Business forms, ownership, tax and corporate structure</x:v>
       </x:c>
       <x:c r="F90" s="109" t="str">
-        <x:v>Revisit equation of value and loans from memory, then target the weakest sub-area.</x:v>
+        <x:v>Revisit business ownership and taxation from memory, then target the weakest sub-area.</x:v>
       </x:c>
       <x:c r="G90" s="109" t="str">
         <x:v>Redo open errors first, then complete another timed mixed set without relying on notes.</x:v>
@@ -5414,22 +5414,22 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="D91" s="109" t="str">
-        <x:v>Annuities and duration</x:v>
+        <x:v>Raising finance</x:v>
       </x:c>
       <x:c r="E91" s="109" t="str">
-        <x:v>Level and increasing annuities, immunisation and duration concepts</x:v>
+        <x:v>Long and short-term finance, share issues, debt, leasing and working capital</x:v>
       </x:c>
       <x:c r="F91" s="109" t="str">
-        <x:v>Create a formula map and a list of common timing traps.</x:v>
+        <x:v>Create a finance-source comparison: cost, risk, control, flexibility and timing.</x:v>
       </x:c>
       <x:c r="G91" s="109" t="str">
-        <x:v>Attempt a timed mixed interest-rate set.</x:v>
+        <x:v>Complete finance-choice questions with a stated recommendation.</x:v>
       </x:c>
       <x:c r="H91" s="109" t="str">
-        <x:v>Use Excel to compare present values under alternative interest-rate scenarios.</x:v>
+        <x:v>Calculate a lease or short-term financing comparison.</x:v>
       </x:c>
       <x:c r="I91" s="109" t="n">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="J91" s="109"/>
       <x:c r="K91" s="109"/>
@@ -5445,13 +5445,13 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="D92" s="109" t="str">
-        <x:v>Annuities and duration</x:v>
+        <x:v>Raising finance</x:v>
       </x:c>
       <x:c r="E92" s="109" t="str">
-        <x:v>Level and increasing annuities, immunisation and duration concepts</x:v>
+        <x:v>Long and short-term finance, share issues, debt, leasing and working capital</x:v>
       </x:c>
       <x:c r="F92" s="109" t="str">
-        <x:v>Revisit annuities and duration from memory, then target the weakest sub-area.</x:v>
+        <x:v>Revisit raising finance from memory, then target the weakest sub-area.</x:v>
       </x:c>
       <x:c r="G92" s="109" t="str">
         <x:v>Redo open errors first, then complete another timed mixed set without relying on notes.</x:v>
@@ -5460,7 +5460,7 @@
         <x:v>Repeat the applied task from a blank file or extend it with an independent check or sensitivity.</x:v>
       </x:c>
       <x:c r="I92" s="109" t="n">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="J92" s="109"/>
       <x:c r="K92" s="109"/>
@@ -5476,22 +5476,22 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D93" s="109" t="str">
-        <x:v>Single-life models</x:v>
+        <x:v>Accounts foundations</x:v>
       </x:c>
       <x:c r="E93" s="109" t="str">
-        <x:v>Survival probabilities, life tables, assurance and annuity values</x:v>
+        <x:v>Statement of profit or loss, financial position and cash flows</x:v>
       </x:c>
       <x:c r="F93" s="109" t="str">
-        <x:v>Convert symbols to a timeline and annotate the contingent payment condition.</x:v>
+        <x:v>Reconstruct the three statements from a blank template.</x:v>
       </x:c>
       <x:c r="G93" s="109" t="str">
-        <x:v>Practise life-contingency questions and rewrite any weak setup.</x:v>
+        <x:v>Complete an accounts-building question and reconcile every total.</x:v>
       </x:c>
       <x:c r="H93" s="109" t="str">
-        <x:v>Calculate life annuity values from a supplied table.</x:v>
+        <x:v>Create an accounts template with balance checks.</x:v>
       </x:c>
       <x:c r="I93" s="109" t="n">
-        <x:v>20</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="J93" s="109"/>
       <x:c r="K93" s="109"/>
@@ -5507,19 +5507,19 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D94" s="109" t="str">
-        <x:v>Multiple lives and decrements</x:v>
+        <x:v>Accounts construction and groups</x:v>
       </x:c>
       <x:c r="E94" s="109" t="str">
-        <x:v>Joint-life, last-survivor, multiple-decrement and select models</x:v>
+        <x:v>Adjustments, group accounts, insurance and bank accounts</x:v>
       </x:c>
       <x:c r="F94" s="109" t="str">
-        <x:v>Write a decision tree for the status and payment trigger.</x:v>
+        <x:v>Write an adjustment checklist before starting any construction question.</x:v>
       </x:c>
       <x:c r="G94" s="109" t="str">
-        <x:v>Attempt a longer multi-part question and audit the notation.</x:v>
+        <x:v>Attempt a longer multi-part construction question.</x:v>
       </x:c>
       <x:c r="H94" s="109" t="str">
-        <x:v>Model decrement probabilities and test that probabilities reconcile.</x:v>
+        <x:v>Use a spreadsheet to separate adjustments from final statements.</x:v>
       </x:c>
       <x:c r="I94" s="109" t="n">
         <x:v>10</x:v>
@@ -5538,13 +5538,13 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D95" s="109" t="str">
-        <x:v>Multiple lives and decrements</x:v>
+        <x:v>Accounts construction and groups</x:v>
       </x:c>
       <x:c r="E95" s="109" t="str">
-        <x:v>Joint-life, last-survivor, multiple-decrement and select models</x:v>
+        <x:v>Adjustments, group accounts, insurance and bank accounts</x:v>
       </x:c>
       <x:c r="F95" s="109" t="str">
-        <x:v>Revisit multiple lives and decrements from memory, then target the weakest sub-area.</x:v>
+        <x:v>Revisit accounts construction and groups from memory, then target the weakest sub-area.</x:v>
       </x:c>
       <x:c r="G95" s="109" t="str">
         <x:v>Redo open errors first, then complete another timed mixed set without relying on notes.</x:v>
@@ -5569,19 +5569,19 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="D96" s="109" t="str">
-        <x:v>Pricing and reserving</x:v>
+        <x:v>Interpreting accounts</x:v>
       </x:c>
       <x:c r="E96" s="109" t="str">
-        <x:v>Net premiums, gross premiums, prospective and retrospective reserves</x:v>
+        <x:v>Ratios, trends, limitations and investor analysis</x:v>
       </x:c>
       <x:c r="F96" s="109" t="str">
-        <x:v>For each formula, state what is being valued, at what time and on what basis.</x:v>
+        <x:v>Use a claim-evidence-conclusion structure for every interpretation paragraph.</x:v>
       </x:c>
       <x:c r="G96" s="109" t="str">
-        <x:v>Complete premium and reserve questions to a strict time budget.</x:v>
+        <x:v>Complete a ratio question, then improve the quality of the narrative answer.</x:v>
       </x:c>
       <x:c r="H96" s="109" t="str">
-        <x:v>Build a reserve roll-forward and investigate each movement.</x:v>
+        <x:v>Calculate and graph a ratio trend from a small data table.</x:v>
       </x:c>
       <x:c r="I96" s="109" t="n">
         <x:v>9</x:v>
@@ -5600,13 +5600,13 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="D97" s="109" t="str">
-        <x:v>Pricing and reserving</x:v>
+        <x:v>Interpreting accounts</x:v>
       </x:c>
       <x:c r="E97" s="109" t="str">
-        <x:v>Net premiums, gross premiums, prospective and retrospective reserves</x:v>
+        <x:v>Ratios, trends, limitations and investor analysis</x:v>
       </x:c>
       <x:c r="F97" s="109" t="str">
-        <x:v>Revisit pricing and reserving from memory, then target the weakest sub-area.</x:v>
+        <x:v>Revisit interpreting accounts from memory, then target the weakest sub-area.</x:v>
       </x:c>
       <x:c r="G97" s="109" t="str">
         <x:v>Redo open errors first, then complete another timed mixed set without relying on notes.</x:v>
@@ -5631,22 +5631,22 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="D98" s="109" t="str">
-        <x:v>Integrated exam practice</x:v>
+        <x:v>Capital structure and growth</x:v>
       </x:c>
       <x:c r="E98" s="109" t="str">
-        <x:v>Mixed CM1 applications, answer structure and weak-area repair</x:v>
+        <x:v>Derivatives, restructuring, WACC, dividend policy and acquisition</x:v>
       </x:c>
       <x:c r="F98" s="109" t="str">
-        <x:v>Choose three recurring error themes and revisit them before comfortable topics.</x:v>
+        <x:v>Create a decision tree for financing and restructuring recommendations.</x:v>
       </x:c>
       <x:c r="G98" s="109" t="str">
-        <x:v>Complete a substantial timed Paper A-style set and self-mark your method.</x:v>
+        <x:v>Complete applied finance questions including a WACC calculation.</x:v>
       </x:c>
       <x:c r="H98" s="109" t="str">
-        <x:v>Complete a timed Excel challenge and check formulas independently.</x:v>
+        <x:v>Build a WACC sensitivity table.</x:v>
       </x:c>
       <x:c r="I98" s="109" t="n">
-        <x:v>13</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="J98" s="109"/>
       <x:c r="K98" s="109"/>
@@ -5662,13 +5662,13 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="D99" s="109" t="str">
-        <x:v>Integrated exam practice</x:v>
+        <x:v>Capital structure and growth</x:v>
       </x:c>
       <x:c r="E99" s="109" t="str">
-        <x:v>Mixed CM1 applications, answer structure and weak-area repair</x:v>
+        <x:v>Derivatives, restructuring, WACC, dividend policy and acquisition</x:v>
       </x:c>
       <x:c r="F99" s="109" t="str">
-        <x:v>Revisit integrated exam practice from memory, then target the weakest sub-area.</x:v>
+        <x:v>Revisit capital structure and growth from memory, then target the weakest sub-area.</x:v>
       </x:c>
       <x:c r="G99" s="109" t="str">
         <x:v>Redo open errors first, then complete another timed mixed set without relying on notes.</x:v>
@@ -5677,7 +5677,7 @@
         <x:v>Repeat the applied task from a blank file or extend it with an independent check or sensitivity.</x:v>
       </x:c>
       <x:c r="I99" s="109" t="n">
-        <x:v>12</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="J99" s="109"/>
       <x:c r="K99" s="109"/>
@@ -5693,22 +5693,22 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="D100" s="109" t="str">
-        <x:v>Mock and consolidation</x:v>
+        <x:v>Project appraisal and mock</x:v>
       </x:c>
       <x:c r="E100" s="109" t="str">
-        <x:v>Whole syllabus, timed practice and final weak-area repair</x:v>
+        <x:v>NPV, IRR, risk, capital projects and whole-syllabus consolidation</x:v>
       </x:c>
       <x:c r="F100" s="109" t="str">
-        <x:v>Create a final formula and notation sheet from memory, then correct it.</x:v>
+        <x:v>Prepare an investment-appraisal checklist and a final error list.</x:v>
       </x:c>
       <x:c r="G100" s="109" t="str">
-        <x:v>Sit a full mock or equivalent timed set, then separate marking from error correction.</x:v>
+        <x:v>Complete a timed mock or equivalent mixed set, then redraft weak written answers.</x:v>
       </x:c>
       <x:c r="H100" s="109" t="str">
-        <x:v>Rebuild the weakest modelling task from a blank workbook.</x:v>
+        <x:v>Build an NPV model and test a key sensitivity.</x:v>
       </x:c>
       <x:c r="I100" s="109" t="n">
-        <x:v>30</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="J100" s="109"/>
       <x:c r="K100" s="109"/>
@@ -5724,22 +5724,22 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="D101" s="109" t="str">
-        <x:v>Theory of interest rates</x:v>
+        <x:v>Governance and objectives</x:v>
       </x:c>
       <x:c r="E101" s="109" t="str">
-        <x:v>Rate conversions, discount functions, force of interest and term structures</x:v>
+        <x:v>Corporate governance, ethics, stakeholders and shareholder wealth</x:v>
       </x:c>
       <x:c r="F101" s="109" t="str">
-        <x:v>Build a one-page rate-conversion sheet and derive each relationship once.</x:v>
+        <x:v>Create a stakeholder-conflict grid and a governance answer plan.</x:v>
       </x:c>
       <x:c r="G101" s="109" t="str">
-        <x:v>Complete short calculations and mark units and timing explicitly.</x:v>
+        <x:v>Write short applied explanations and self-check for a direct conclusion.</x:v>
       </x:c>
       <x:c r="H101" s="109" t="str">
-        <x:v>Create a simple cashflow-discounting model in Excel.</x:v>
+        <x:v>Build a one-page summary of key distinctions and common command words.</x:v>
       </x:c>
       <x:c r="I101" s="109" t="n">
-        <x:v>10</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="J101" s="109"/>
       <x:c r="K101" s="109"/>
@@ -5755,13 +5755,13 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="D102" s="109" t="str">
-        <x:v>Theory of interest rates</x:v>
+        <x:v>Governance and objectives</x:v>
       </x:c>
       <x:c r="E102" s="109" t="str">
-        <x:v>Rate conversions, discount functions, force of interest and term structures</x:v>
+        <x:v>Corporate governance, ethics, stakeholders and shareholder wealth</x:v>
       </x:c>
       <x:c r="F102" s="109" t="str">
-        <x:v>Revisit theory of interest rates from memory, then target the weakest sub-area.</x:v>
+        <x:v>Revisit governance and objectives from memory, then target the weakest sub-area.</x:v>
       </x:c>
       <x:c r="G102" s="109" t="str">
         <x:v>Redo open errors first, then complete another timed mixed set without relying on notes.</x:v>
@@ -5770,7 +5770,7 @@
         <x:v>Repeat the applied task from a blank file or extend it with an independent check or sensitivity.</x:v>
       </x:c>
       <x:c r="I102" s="109" t="n">
-        <x:v>10</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="J102" s="109"/>
       <x:c r="K102" s="109"/>
@@ -5786,19 +5786,19 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="D103" s="109" t="str">
-        <x:v>Equation of value and loans</x:v>
+        <x:v>Business ownership and taxation</x:v>
       </x:c>
       <x:c r="E103" s="109" t="str">
-        <x:v>Cashflow valuation, loans, outstanding balances, bonds and yield</x:v>
+        <x:v>Business forms, ownership, tax and corporate structure</x:v>
       </x:c>
       <x:c r="F103" s="109" t="str">
-        <x:v>Draw every cashflow timeline before calculating and practise two methods for loan questions.</x:v>
+        <x:v>Compare each legal form by ownership, risk, capital and control.</x:v>
       </x:c>
       <x:c r="G103" s="109" t="str">
-        <x:v>Complete mixed loan and bond questions under time pressure.</x:v>
+        <x:v>Complete scenario questions requiring a justified recommendation.</x:v>
       </x:c>
       <x:c r="H103" s="109" t="str">
-        <x:v>Build a loan schedule with a rate input and balance check.</x:v>
+        <x:v>Use a simple table to compare tax or cashflow implications.</x:v>
       </x:c>
       <x:c r="I103" s="109" t="n">
         <x:v>9</x:v>
@@ -5817,13 +5817,13 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="D104" s="109" t="str">
-        <x:v>Equation of value and loans</x:v>
+        <x:v>Business ownership and taxation</x:v>
       </x:c>
       <x:c r="E104" s="109" t="str">
-        <x:v>Cashflow valuation, loans, outstanding balances, bonds and yield</x:v>
+        <x:v>Business forms, ownership, tax and corporate structure</x:v>
       </x:c>
       <x:c r="F104" s="109" t="str">
-        <x:v>Revisit equation of value and loans from memory, then target the weakest sub-area.</x:v>
+        <x:v>Revisit business ownership and taxation from memory, then target the weakest sub-area.</x:v>
       </x:c>
       <x:c r="G104" s="109" t="str">
         <x:v>Redo open errors first, then complete another timed mixed set without relying on notes.</x:v>
@@ -5848,22 +5848,22 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="D105" s="109" t="str">
-        <x:v>Annuities and duration</x:v>
+        <x:v>Raising finance</x:v>
       </x:c>
       <x:c r="E105" s="109" t="str">
-        <x:v>Level and increasing annuities, immunisation and duration concepts</x:v>
+        <x:v>Long and short-term finance, share issues, debt, leasing and working capital</x:v>
       </x:c>
       <x:c r="F105" s="109" t="str">
-        <x:v>Create a formula map and a list of common timing traps.</x:v>
+        <x:v>Create a finance-source comparison: cost, risk, control, flexibility and timing.</x:v>
       </x:c>
       <x:c r="G105" s="109" t="str">
-        <x:v>Attempt a timed mixed interest-rate set.</x:v>
+        <x:v>Complete finance-choice questions with a stated recommendation.</x:v>
       </x:c>
       <x:c r="H105" s="109" t="str">
-        <x:v>Use Excel to compare present values under alternative interest-rate scenarios.</x:v>
+        <x:v>Calculate a lease or short-term financing comparison.</x:v>
       </x:c>
       <x:c r="I105" s="109" t="n">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="J105" s="109"/>
       <x:c r="K105" s="109"/>
@@ -5879,13 +5879,13 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="D106" s="109" t="str">
-        <x:v>Annuities and duration</x:v>
+        <x:v>Raising finance</x:v>
       </x:c>
       <x:c r="E106" s="109" t="str">
-        <x:v>Level and increasing annuities, immunisation and duration concepts</x:v>
+        <x:v>Long and short-term finance, share issues, debt, leasing and working capital</x:v>
       </x:c>
       <x:c r="F106" s="109" t="str">
-        <x:v>Revisit annuities and duration from memory, then target the weakest sub-area.</x:v>
+        <x:v>Revisit raising finance from memory, then target the weakest sub-area.</x:v>
       </x:c>
       <x:c r="G106" s="109" t="str">
         <x:v>Redo open errors first, then complete another timed mixed set without relying on notes.</x:v>
@@ -5894,7 +5894,7 @@
         <x:v>Repeat the applied task from a blank file or extend it with an independent check or sensitivity.</x:v>
       </x:c>
       <x:c r="I106" s="109" t="n">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="J106" s="109"/>
       <x:c r="K106" s="109"/>
@@ -5910,22 +5910,22 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D107" s="109" t="str">
-        <x:v>Single-life models</x:v>
+        <x:v>Accounts foundations</x:v>
       </x:c>
       <x:c r="E107" s="109" t="str">
-        <x:v>Survival probabilities, life tables, assurance and annuity values</x:v>
+        <x:v>Statement of profit or loss, financial position and cash flows</x:v>
       </x:c>
       <x:c r="F107" s="109" t="str">
-        <x:v>Convert symbols to a timeline and annotate the contingent payment condition.</x:v>
+        <x:v>Reconstruct the three statements from a blank template.</x:v>
       </x:c>
       <x:c r="G107" s="109" t="str">
-        <x:v>Practise life-contingency questions and rewrite any weak setup.</x:v>
+        <x:v>Complete an accounts-building question and reconcile every total.</x:v>
       </x:c>
       <x:c r="H107" s="109" t="str">
-        <x:v>Calculate life annuity values from a supplied table.</x:v>
+        <x:v>Create an accounts template with balance checks.</x:v>
       </x:c>
       <x:c r="I107" s="109" t="n">
-        <x:v>10</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="J107" s="109"/>
       <x:c r="K107" s="109"/>
@@ -5941,13 +5941,13 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D108" s="109" t="str">
-        <x:v>Single-life models</x:v>
+        <x:v>Accounts foundations</x:v>
       </x:c>
       <x:c r="E108" s="109" t="str">
-        <x:v>Survival probabilities, life tables, assurance and annuity values</x:v>
+        <x:v>Statement of profit or loss, financial position and cash flows</x:v>
       </x:c>
       <x:c r="F108" s="109" t="str">
-        <x:v>Revisit single-life models from memory, then target the weakest sub-area.</x:v>
+        <x:v>Revisit accounts foundations from memory, then target the weakest sub-area.</x:v>
       </x:c>
       <x:c r="G108" s="109" t="str">
         <x:v>Redo open errors first, then complete another timed mixed set without relying on notes.</x:v>
@@ -5956,7 +5956,7 @@
         <x:v>Repeat the applied task from a blank file or extend it with an independent check or sensitivity.</x:v>
       </x:c>
       <x:c r="I108" s="109" t="n">
-        <x:v>10</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="J108" s="109"/>
       <x:c r="K108" s="109"/>
@@ -5972,19 +5972,19 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D109" s="109" t="str">
-        <x:v>Multiple lives and decrements</x:v>
+        <x:v>Accounts construction and groups</x:v>
       </x:c>
       <x:c r="E109" s="109" t="str">
-        <x:v>Joint-life, last-survivor, multiple-decrement and select models</x:v>
+        <x:v>Adjustments, group accounts, insurance and bank accounts</x:v>
       </x:c>
       <x:c r="F109" s="109" t="str">
-        <x:v>Write a decision tree for the status and payment trigger.</x:v>
+        <x:v>Write an adjustment checklist before starting any construction question.</x:v>
       </x:c>
       <x:c r="G109" s="109" t="str">
-        <x:v>Attempt a longer multi-part question and audit the notation.</x:v>
+        <x:v>Attempt a longer multi-part construction question.</x:v>
       </x:c>
       <x:c r="H109" s="109" t="str">
-        <x:v>Model decrement probabilities and test that probabilities reconcile.</x:v>
+        <x:v>Use a spreadsheet to separate adjustments from final statements.</x:v>
       </x:c>
       <x:c r="I109" s="109" t="n">
         <x:v>10</x:v>
@@ -6003,13 +6003,13 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="D110" s="109" t="str">
-        <x:v>Multiple lives and decrements</x:v>
+        <x:v>Accounts construction and groups</x:v>
       </x:c>
       <x:c r="E110" s="109" t="str">
-        <x:v>Joint-life, last-survivor, multiple-decrement and select models</x:v>
+        <x:v>Adjustments, group accounts, insurance and bank accounts</x:v>
       </x:c>
       <x:c r="F110" s="109" t="str">
-        <x:v>Revisit multiple lives and decrements from memory, then target the weakest sub-area.</x:v>
+        <x:v>Revisit accounts construction and groups from memory, then target the weakest sub-area.</x:v>
       </x:c>
       <x:c r="G110" s="109" t="str">
         <x:v>Redo open errors first, then complete another timed mixed set without relying on notes.</x:v>
@@ -6034,19 +6034,19 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="D111" s="109" t="str">
-        <x:v>Pricing and reserving</x:v>
+        <x:v>Interpreting accounts</x:v>
       </x:c>
       <x:c r="E111" s="109" t="str">
-        <x:v>Net premiums, gross premiums, prospective and retrospective reserves</x:v>
+        <x:v>Ratios, trends, limitations and investor analysis</x:v>
       </x:c>
       <x:c r="F111" s="109" t="str">
-        <x:v>For each formula, state what is being valued, at what time and on what basis.</x:v>
+        <x:v>Use a claim-evidence-conclusion structure for every interpretation paragraph.</x:v>
       </x:c>
       <x:c r="G111" s="109" t="str">
-        <x:v>Complete premium and reserve questions to a strict time budget.</x:v>
+        <x:v>Complete a ratio question, then improve the quality of the narrative answer.</x:v>
       </x:c>
       <x:c r="H111" s="109" t="str">
-        <x:v>Build a reserve roll-forward and investigate each movement.</x:v>
+        <x:v>Calculate and graph a ratio trend from a small data table.</x:v>
       </x:c>
       <x:c r="I111" s="109" t="n">
         <x:v>9</x:v>
@@ -6065,13 +6065,13 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="D112" s="109" t="str">
-        <x:v>Pricing and reserving</x:v>
+        <x:v>Interpreting accounts</x:v>
       </x:c>
       <x:c r="E112" s="109" t="str">
-        <x:v>Net premiums, gross premiums, prospective and retrospective reserves</x:v>
+        <x:v>Ratios, trends, limitations and investor analysis</x:v>
       </x:c>
       <x:c r="F112" s="109" t="str">
-        <x:v>Revisit pricing and reserving from memory, then target the weakest sub-area.</x:v>
+        <x:v>Revisit interpreting accounts from memory, then target the weakest sub-area.</x:v>
       </x:c>
       <x:c r="G112" s="109" t="str">
         <x:v>Redo open errors first, then complete another timed mixed set without relying on notes.</x:v>
@@ -6096,22 +6096,22 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="D113" s="109" t="str">
-        <x:v>Integrated exam practice</x:v>
+        <x:v>Capital structure and growth</x:v>
       </x:c>
       <x:c r="E113" s="109" t="str">
-        <x:v>Mixed CM1 applications, answer structure and weak-area repair</x:v>
+        <x:v>Derivatives, restructuring, WACC, dividend policy and acquisition</x:v>
       </x:c>
       <x:c r="F113" s="109" t="str">
-        <x:v>Choose three recurring error themes and revisit them before comfortable topics.</x:v>
+        <x:v>Create a decision tree for financing and restructuring recommendations.</x:v>
       </x:c>
       <x:c r="G113" s="109" t="str">
-        <x:v>Complete a substantial timed Paper A-style set and self-mark your method.</x:v>
+        <x:v>Complete applied finance questions including a WACC calculation.</x:v>
       </x:c>
       <x:c r="H113" s="109" t="str">
-        <x:v>Complete a timed Excel challenge and check formulas independently.</x:v>
+        <x:v>Build a WACC sensitivity table.</x:v>
       </x:c>
       <x:c r="I113" s="109" t="n">
-        <x:v>13</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="J113" s="109"/>
       <x:c r="K113" s="109"/>
@@ -6127,13 +6127,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="D114" s="109" t="str">
-        <x:v>Integrated exam practice</x:v>
+        <x:v>Capital structure and growth</x:v>
       </x:c>
       <x:c r="E114" s="109" t="str">
-        <x:v>Mixed CM1 applications, answer structure and weak-area repair</x:v>
+        <x:v>Derivatives, restructuring, WACC, dividend policy and acquisition</x:v>
       </x:c>
       <x:c r="F114" s="109" t="str">
-        <x:v>Revisit integrated exam practice from memory, then target the weakest sub-area.</x:v>
+        <x:v>Revisit capital structure and growth from memory, then target the weakest sub-area.</x:v>
       </x:c>
       <x:c r="G114" s="109" t="str">
         <x:v>Redo open errors first, then complete another timed mixed set without relying on notes.</x:v>
@@ -6142,7 +6142,7 @@
         <x:v>Repeat the applied task from a blank file or extend it with an independent check or sensitivity.</x:v>
       </x:c>
       <x:c r="I114" s="109" t="n">
-        <x:v>12</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="J114" s="109"/>
       <x:c r="K114" s="109"/>
@@ -6158,22 +6158,22 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="D115" s="109" t="str">
-        <x:v>Mock and consolidation</x:v>
+        <x:v>Project appraisal and mock</x:v>
       </x:c>
       <x:c r="E115" s="109" t="str">
-        <x:v>Whole syllabus, timed practice and final weak-area repair</x:v>
+        <x:v>NPV, IRR, risk, capital projects and whole-syllabus consolidation</x:v>
       </x:c>
       <x:c r="F115" s="109" t="str">
-        <x:v>Create a final formula and notation sheet from memory, then correct it.</x:v>
+        <x:v>Prepare an investment-appraisal checklist and a final error list.</x:v>
       </x:c>
       <x:c r="G115" s="109" t="str">
-        <x:v>Sit a full mock or equivalent timed set, then separate marking from error correction.</x:v>
+        <x:v>Complete a timed mock or equivalent mixed set, then redraft weak written answers.</x:v>
       </x:c>
       <x:c r="H115" s="109" t="str">
-        <x:v>Rebuild the weakest modelling task from a blank workbook.</x:v>
+        <x:v>Build an NPV model and test a key sensitivity.</x:v>
       </x:c>
       <x:c r="I115" s="109" t="n">
-        <x:v>30</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="J115" s="109"/>
       <x:c r="K115" s="109"/>
@@ -6189,22 +6189,22 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="D116" s="109" t="str">
-        <x:v>Theory of interest rates</x:v>
+        <x:v>Governance and objectives</x:v>
       </x:c>
       <x:c r="E116" s="109" t="str">
-        <x:v>Rate conversions, discount functions, force of interest and term structures</x:v>
+        <x:v>Corporate governance, ethics, stakeholders and shareholder wealth</x:v>
       </x:c>
       <x:c r="F116" s="109" t="str">
-        <x:v>Build a one-page rate-conversion sheet and derive each relationship once.</x:v>
+        <x:v>Create a stakeholder-conflict grid and a governance answer plan.</x:v>
       </x:c>
       <x:c r="G116" s="109" t="str">
-        <x:v>Complete short calculations and mark units and timing explicitly.</x:v>
+        <x:v>Write short applied explanations and self-check for a direct conclusion.</x:v>
       </x:c>
       <x:c r="H116" s="109" t="str">
-        <x:v>Create a simple cashflow-discounting model in Excel.</x:v>
+        <x:v>Build a one-page summary of key distinctions and common command words.</x:v>
       </x:c>
       <x:c r="I116" s="109" t="n">
-        <x:v>10</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="J116" s="109"/>
       <x:c r="K116" s="109"/>
@@ -6220,13 +6220,13 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="D117" s="109" t="str">
-        <x:v>Theory of interest rates</x:v>
+        <x:v>Governance and objectives</x:v>
       </x:c>
       <x:c r="E117" s="109" t="str">
-        <x:v>Rate conversions, discount functions, force of interest and term structures</x:v>
+        <x:v>Corporate governance, ethics, stakeholders and shareholder wealth</x:v>
       </x:c>
       <x:c r="F117" s="109" t="str">
-        <x:v>Revisit theory of interest rates from memory, then target the weakest sub-area.</x:v>
+        <x:v>Revisit governance and objectives from memory, then target the weakest sub-area.</x:v>
       </x:c>
       <x:c r="G117" s="109" t="str">
         <x:v>Redo open errors first, then complete another timed mixed set without relying on notes.</x:v>
@@ -6235,7 +6235,7 @@
         <x:v>Repeat the applied task from a blank file or extend it with an independent check or sensitivity.</x:v>
       </x:c>
       <x:c r="I117" s="109" t="n">
-        <x:v>10</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="J117" s="109"/>
       <x:c r="K117" s="109"/>
@@ -6251,19 +6251,19 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="D118" s="109" t="str">
-        <x:v>Equation of value and loans</x:v>
+        <x:v>Business ownership and taxation</x:v>
       </x:c>
       <x:c r="E118" s="109" t="str">
-        <x:v>Cashflow valuation, loans, outstanding balances, bonds and yield</x:v>
+        <x:v>Business forms, ownership, tax and corporate structure</x:v>
       </x:c>
       <x:c r="F118" s="109" t="str">
-        <x:v>Draw every cashflow timeline before calculating and practise two methods for loan questions.</x:v>
+        <x:v>Compare each legal form by ownership, risk, capital and control.</x:v>
       </x:c>
       <x:c r="G118" s="109" t="str">
-        <x:v>Complete mixed loan and bond questions under time pressure.</x:v>
+        <x:v>Complete scenario questions requiring a justified recommendation.</x:v>
       </x:c>
       <x:c r="H118" s="109" t="str">
-        <x:v>Build a loan schedule with a rate input and balance check.</x:v>
+        <x:v>Use a simple table to compare tax or cashflow implications.</x:v>
       </x:c>
       <x:c r="I118" s="109" t="n">
         <x:v>9</x:v>
@@ -6282,13 +6282,13 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="D119" s="109" t="str">
-        <x:v>Equation of value and loans</x:v>
+        <x:v>Business ownership and taxation</x:v>
       </x:c>
       <x:c r="E119" s="109" t="str">
-        <x:v>Cashflow valuation, loans, outstanding balances, bonds and yield</x:v>
+        <x:v>Business forms, ownership, tax and corporate structure</x:v>
       </x:c>
       <x:c r="F119" s="109" t="str">
-        <x:v>Revisit equation of value and loans from memory, then target the weakest sub-area.</x:v>
+        <x:v>Revisit business ownership and taxation from memory, then target the weakest sub-area.</x:v>
       </x:c>
       <x:c r="G119" s="109" t="str">
         <x:v>Redo open errors first, then complete another timed mixed set without relying on notes.</x:v>
@@ -6313,22 +6313,22 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="D120" s="109" t="str">
-        <x:v>Annuities and duration</x:v>
+        <x:v>Raising finance</x:v>
       </x:c>
       <x:c r="E120" s="109" t="str">
-        <x:v>Level and increasing annuities, immunisation and duration concepts</x:v>
+        <x:v>Long and short-term finance, share issues, debt, leasing and working capital</x:v>
       </x:c>
       <x:c r="F120" s="109" t="str">
-        <x:v>Create a formula map and a list of common timing traps.</x:v>
+        <x:v>Create a finance-source comparison: cost, risk, control, flexibility and timing.</x:v>
       </x:c>
       <x:c r="G120" s="109" t="str">
-        <x:v>Attempt a timed mixed interest-rate set.</x:v>
+        <x:v>Complete finance-choice questions with a stated recommendation.</x:v>
       </x:c>
       <x:c r="H120" s="109" t="str">
-        <x:v>Use Excel to compare present values under alternative interest-rate scenarios.</x:v>
+        <x:v>Calculate a lease or short-term financing comparison.</x:v>
       </x:c>
       <x:c r="I120" s="109" t="n">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="J120" s="109"/>
       <x:c r="K120" s="109"/>
@@ -6344,13 +6344,13 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="D121" s="109" t="str">
-        <x:v>Annuities and duration</x:v>
+        <x:v>Raising finance</x:v>
       </x:c>
       <x:c r="E121" s="109" t="str">
-        <x:v>Level and increasing annuities, immunisation and duration concepts</x:v>
+        <x:v>Long and short-term finance, share issues, debt, leasing and working capital</x:v>
       </x:c>
       <x:c r="F121" s="109" t="str">
-        <x:v>Revisit annuities and duration from memory, then target the weakest sub-area.</x:v>
+        <x:v>Revisit raising finance from memory, then target the weakest sub-area.</x:v>
       </x:c>
       <x:c r="G121" s="109" t="str">
         <x:v>Redo open errors first, then complete another timed mixed set without relying on notes.</x:v>
@@ -6359,7 +6359,7 @@
         <x:v>Repeat the applied task from a blank file or extend it with an independent check or sensitivity.</x:v>
       </x:c>
       <x:c r="I121" s="109" t="n">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="J121" s="109"/>
       <x:c r="K121" s="109"/>
@@ -6375,22 +6375,22 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D122" s="109" t="str">
-        <x:v>Single-life models</x:v>
+        <x:v>Accounts foundations</x:v>
       </x:c>
       <x:c r="E122" s="109" t="str">
-        <x:v>Survival probabilities, life tables, assurance and annuity values</x:v>
+        <x:v>Statement of profit or loss, financial position and cash flows</x:v>
       </x:c>
       <x:c r="F122" s="109" t="str">
-        <x:v>Convert symbols to a timeline and annotate the contingent payment condition.</x:v>
+        <x:v>Reconstruct the three statements from a blank template.</x:v>
       </x:c>
       <x:c r="G122" s="109" t="str">
-        <x:v>Practise life-contingency questions and rewrite any weak setup.</x:v>
+        <x:v>Complete an accounts-building question and reconcile every total.</x:v>
       </x:c>
       <x:c r="H122" s="109" t="str">
-        <x:v>Calculate life annuity values from a supplied table.</x:v>
+        <x:v>Create an accounts template with balance checks.</x:v>
       </x:c>
       <x:c r="I122" s="109" t="n">
-        <x:v>10</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="J122" s="109"/>
       <x:c r="K122" s="109"/>
@@ -6406,13 +6406,13 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D123" s="109" t="str">
-        <x:v>Single-life models</x:v>
+        <x:v>Accounts foundations</x:v>
       </x:c>
       <x:c r="E123" s="109" t="str">
-        <x:v>Survival probabilities, life tables, assurance and annuity values</x:v>
+        <x:v>Statement of profit or loss, financial position and cash flows</x:v>
       </x:c>
       <x:c r="F123" s="109" t="str">
-        <x:v>Revisit single-life models from memory, then target the weakest sub-area.</x:v>
+        <x:v>Revisit accounts foundations from memory, then target the weakest sub-area.</x:v>
       </x:c>
       <x:c r="G123" s="109" t="str">
         <x:v>Redo open errors first, then complete another timed mixed set without relying on notes.</x:v>
@@ -6421,7 +6421,7 @@
         <x:v>Repeat the applied task from a blank file or extend it with an independent check or sensitivity.</x:v>
       </x:c>
       <x:c r="I123" s="109" t="n">
-        <x:v>10</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="J123" s="109"/>
       <x:c r="K123" s="109"/>
@@ -6437,19 +6437,19 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D124" s="109" t="str">
-        <x:v>Multiple lives and decrements</x:v>
+        <x:v>Accounts construction and groups</x:v>
       </x:c>
       <x:c r="E124" s="109" t="str">
-        <x:v>Joint-life, last-survivor, multiple-decrement and select models</x:v>
+        <x:v>Adjustments, group accounts, insurance and bank accounts</x:v>
       </x:c>
       <x:c r="F124" s="109" t="str">
-        <x:v>Write a decision tree for the status and payment trigger.</x:v>
+        <x:v>Write an adjustment checklist before starting any construction question.</x:v>
       </x:c>
       <x:c r="G124" s="109" t="str">
-        <x:v>Attempt a longer multi-part question and audit the notation.</x:v>
+        <x:v>Attempt a longer multi-part construction question.</x:v>
       </x:c>
       <x:c r="H124" s="109" t="str">
-        <x:v>Model decrement probabilities and test that probabilities reconcile.</x:v>
+        <x:v>Use a spreadsheet to separate adjustments from final statements.</x:v>
       </x:c>
       <x:c r="I124" s="109" t="n">
         <x:v>10</x:v>
@@ -6468,13 +6468,13 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="D125" s="109" t="str">
-        <x:v>Multiple lives and decrements</x:v>
+        <x:v>Accounts construction and groups</x:v>
       </x:c>
       <x:c r="E125" s="109" t="str">
-        <x:v>Joint-life, last-survivor, multiple-decrement and select models</x:v>
+        <x:v>Adjustments, group accounts, insurance and bank accounts</x:v>
       </x:c>
       <x:c r="F125" s="109" t="str">
-        <x:v>Revisit multiple lives and decrements from memory, then target the weakest sub-area.</x:v>
+        <x:v>Revisit accounts construction and groups from memory, then target the weakest sub-area.</x:v>
       </x:c>
       <x:c r="G125" s="109" t="str">
         <x:v>Redo open errors first, then complete another timed mixed set without relying on notes.</x:v>
@@ -6499,19 +6499,19 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="D126" s="109" t="str">
-        <x:v>Pricing and reserving</x:v>
+        <x:v>Interpreting accounts</x:v>
       </x:c>
       <x:c r="E126" s="109" t="str">
-        <x:v>Net premiums, gross premiums, prospective and retrospective reserves</x:v>
+        <x:v>Ratios, trends, limitations and investor analysis</x:v>
       </x:c>
       <x:c r="F126" s="109" t="str">
-        <x:v>For each formula, state what is being valued, at what time and on what basis.</x:v>
+        <x:v>Use a claim-evidence-conclusion structure for every interpretation paragraph.</x:v>
       </x:c>
       <x:c r="G126" s="109" t="str">
-        <x:v>Complete premium and reserve questions to a strict time budget.</x:v>
+        <x:v>Complete a ratio question, then improve the quality of the narrative answer.</x:v>
       </x:c>
       <x:c r="H126" s="109" t="str">
-        <x:v>Build a reserve roll-forward and investigate each movement.</x:v>
+        <x:v>Calculate and graph a ratio trend from a small data table.</x:v>
       </x:c>
       <x:c r="I126" s="109" t="n">
         <x:v>9</x:v>
@@ -6530,13 +6530,13 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="D127" s="109" t="str">
-        <x:v>Pricing and reserving</x:v>
+        <x:v>Interpreting accounts</x:v>
       </x:c>
       <x:c r="E127" s="109" t="str">
-        <x:v>Net premiums, gross premiums, prospective and retrospective reserves</x:v>
+        <x:v>Ratios, trends, limitations and investor analysis</x:v>
       </x:c>
       <x:c r="F127" s="109" t="str">
-        <x:v>Revisit pricing and reserving from memory, then target the weakest sub-area.</x:v>
+        <x:v>Revisit interpreting accounts from memory, then target the weakest sub-area.</x:v>
       </x:c>
       <x:c r="G127" s="109" t="str">
         <x:v>Redo open errors first, then complete another timed mixed set without relying on notes.</x:v>
@@ -6561,22 +6561,22 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="D128" s="109" t="str">
-        <x:v>Integrated exam practice</x:v>
+        <x:v>Capital structure and growth</x:v>
       </x:c>
       <x:c r="E128" s="109" t="str">
-        <x:v>Mixed CM1 applications, answer structure and weak-area repair</x:v>
+        <x:v>Derivatives, restructuring, WACC, dividend policy and acquisition</x:v>
       </x:c>
       <x:c r="F128" s="109" t="str">
-        <x:v>Choose three recurring error themes and revisit them before comfortable topics.</x:v>
+        <x:v>Create a decision tree for financing and restructuring recommendations.</x:v>
       </x:c>
       <x:c r="G128" s="109" t="str">
-        <x:v>Complete a substantial timed Paper A-style set and self-mark your method.</x:v>
+        <x:v>Complete applied finance questions including a WACC calculation.</x:v>
       </x:c>
       <x:c r="H128" s="109" t="str">
-        <x:v>Complete a timed Excel challenge and check formulas independently.</x:v>
+        <x:v>Build a WACC sensitivity table.</x:v>
       </x:c>
       <x:c r="I128" s="109" t="n">
-        <x:v>13</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="J128" s="109"/>
       <x:c r="K128" s="109"/>
@@ -6592,13 +6592,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="D129" s="109" t="str">
-        <x:v>Integrated exam practice</x:v>
+        <x:v>Capital structure and growth</x:v>
       </x:c>
       <x:c r="E129" s="109" t="str">
-        <x:v>Mixed CM1 applications, answer structure and weak-area repair</x:v>
+        <x:v>Derivatives, restructuring, WACC, dividend policy and acquisition</x:v>
       </x:c>
       <x:c r="F129" s="109" t="str">
-        <x:v>Revisit integrated exam practice from memory, then target the weakest sub-area.</x:v>
+        <x:v>Revisit capital structure and growth from memory, then target the weakest sub-area.</x:v>
       </x:c>
       <x:c r="G129" s="109" t="str">
         <x:v>Redo open errors first, then complete another timed mixed set without relying on notes.</x:v>
@@ -6607,7 +6607,7 @@
         <x:v>Repeat the applied task from a blank file or extend it with an independent check or sensitivity.</x:v>
       </x:c>
       <x:c r="I129" s="109" t="n">
-        <x:v>12</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="J129" s="109"/>
       <x:c r="K129" s="109"/>
@@ -6623,22 +6623,22 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="D130" s="109" t="str">
-        <x:v>Mock and consolidation</x:v>
+        <x:v>Project appraisal and mock</x:v>
       </x:c>
       <x:c r="E130" s="109" t="str">
-        <x:v>Whole syllabus, timed practice and final weak-area repair</x:v>
+        <x:v>NPV, IRR, risk, capital projects and whole-syllabus consolidation</x:v>
       </x:c>
       <x:c r="F130" s="109" t="str">
-        <x:v>Create a final formula and notation sheet from memory, then correct it.</x:v>
+        <x:v>Prepare an investment-appraisal checklist and a final error list.</x:v>
       </x:c>
       <x:c r="G130" s="109" t="str">
-        <x:v>Sit a full mock or equivalent timed set, then separate marking from error correction.</x:v>
+        <x:v>Complete a timed mock or equivalent mixed set, then redraft weak written answers.</x:v>
       </x:c>
       <x:c r="H130" s="109" t="str">
-        <x:v>Rebuild the weakest modelling task from a blank workbook.</x:v>
+        <x:v>Build an NPV model and test a key sensitivity.</x:v>
       </x:c>
       <x:c r="I130" s="109" t="n">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J130" s="109"/>
       <x:c r="K130" s="109"/>
@@ -6654,13 +6654,13 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="D131" s="109" t="str">
-        <x:v>Mock and consolidation</x:v>
+        <x:v>Project appraisal and mock</x:v>
       </x:c>
       <x:c r="E131" s="109" t="str">
-        <x:v>Whole syllabus, timed practice and final weak-area repair</x:v>
+        <x:v>NPV, IRR, risk, capital projects and whole-syllabus consolidation</x:v>
       </x:c>
       <x:c r="F131" s="109" t="str">
-        <x:v>Revisit mock and consolidation from memory, then target the weakest sub-area.</x:v>
+        <x:v>Revisit project appraisal and mock from memory, then target the weakest sub-area.</x:v>
       </x:c>
       <x:c r="G131" s="109" t="str">
         <x:v>Redo open errors first, then complete another timed mixed set without relying on notes.</x:v>
@@ -6669,7 +6669,7 @@
         <x:v>Repeat the applied task from a blank file or extend it with an independent check or sensitivity.</x:v>
       </x:c>
       <x:c r="I131" s="109" t="n">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J131" s="109"/>
       <x:c r="K131" s="109"/>
